--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,423 +656,448 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44751</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44639</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44555</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44387</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44275</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44191</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44107</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44023</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43911</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43743</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43659</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43547</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43379</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43295</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43183</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43015</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42931</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42819</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>65500</v>
+      </c>
+      <c r="F8" s="3">
         <v>73400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>67800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>56900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>72100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>74900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>94300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>72400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>73400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>81300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>99700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>59200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>74800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>78100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>83500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>37300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>47000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>45800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>55600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>32100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>51000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>44000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>48700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>32100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>52200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>41900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>53900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>31900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>49800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>49600</v>
+      </c>
+      <c r="F9" s="3">
         <v>55200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>51100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>45900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>56000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>61300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>70600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>52300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>57100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>63000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>74600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>41800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>56900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>54500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>60300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>27100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>36200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>35700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>42700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>23600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>38800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>31600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>37200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>23200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>40200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>30500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>40800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>23600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>39600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>15900</v>
+      </c>
+      <c r="F10" s="3">
         <v>18200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>16700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>11000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>16100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>13600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>23700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>20100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>16300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>18300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>25100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>17400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>17900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>23600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>23200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>10200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>10800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>10100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>12900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>8500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>12200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>12400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>11500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>8900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>12000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>11400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>13100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>8300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>10200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1105,8 +1130,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1197,8 +1224,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1289,8 +1322,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1373,16 +1412,22 @@
         <v>0</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>-300</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1396,34 +1441,34 @@
         <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
         <v>600</v>
       </c>
       <c r="I15" s="3">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
       </c>
       <c r="K15" s="3">
+        <v>900</v>
+      </c>
+      <c r="L15" s="3">
+        <v>600</v>
+      </c>
+      <c r="M15" s="3">
         <v>400</v>
-      </c>
-      <c r="L15" s="3">
-        <v>400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>600</v>
       </c>
       <c r="N15" s="3">
         <v>400</v>
       </c>
       <c r="O15" s="3">
+        <v>600</v>
+      </c>
+      <c r="P15" s="3">
         <v>400</v>
-      </c>
-      <c r="P15" s="3">
-        <v>300</v>
       </c>
       <c r="Q15" s="3">
         <v>400</v>
@@ -1432,25 +1477,25 @@
         <v>300</v>
       </c>
       <c r="S15" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T15" s="3">
         <v>300</v>
       </c>
       <c r="U15" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="V15" s="3">
         <v>300</v>
       </c>
       <c r="W15" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="X15" s="3">
         <v>300</v>
       </c>
       <c r="Y15" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z15" s="3">
         <v>300</v>
@@ -1459,22 +1504,28 @@
         <v>400</v>
       </c>
       <c r="AB15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC15" s="3">
         <v>400</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>500</v>
       </c>
       <c r="AD15" s="3">
         <v>400</v>
       </c>
       <c r="AE15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AF15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1504,192 +1555,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>60500</v>
+      </c>
+      <c r="F17" s="3">
         <v>66900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>61500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>56800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>67300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>70700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>86100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>63400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>67000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>73600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>89000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>52100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>67800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>65300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>72700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>34900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>43500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>42900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>53200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>31700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>46000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>38800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>46700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>30400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>47100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>37800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>50600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>29600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>46100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F18" s="3">
         <v>6500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>6300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>4800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>4200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>8200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>9000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>6400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>7700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>10700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>7100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>7000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>12800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>10800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>2900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>5000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>5200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>2000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>5100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>4100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>3300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>2300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>3700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1722,8 +1787,10 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1737,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1752,13 +1819,13 @@
         <v>100</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1791,164 +1858,176 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>13100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F21" s="3">
         <v>7900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>7700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>1600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>5800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>5800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>10300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>10500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>7300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>9000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>12300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>8300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>7700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>13900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>12200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>3400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>4300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>3800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>1300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>5800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>6100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>16200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>6800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>5700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>4700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>3100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>5400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F22" s="3">
         <v>1300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>1600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>1000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
@@ -1960,7 +2039,7 @@
         <v>100</v>
       </c>
       <c r="T22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U22" s="3">
         <v>100</v>
@@ -1969,16 +2048,16 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>200</v>
@@ -1998,192 +2077,210 @@
       <c r="AF22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F23" s="3">
         <v>5100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>7300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>8500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>6000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>10300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>6900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>12800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>10800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>5000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>5100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>14900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>5800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>4500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>3100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>2000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>4400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="E24" s="3">
         <v>1000</v>
       </c>
       <c r="F24" s="3">
+        <v>900</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>2100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>2800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>1400</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>600</v>
       </c>
       <c r="AE24" s="3">
         <v>1000</v>
       </c>
       <c r="AF24" s="3">
+        <v>600</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2274,192 +2371,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F26" s="3">
         <v>4300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>6700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>5100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>10200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>8700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>3600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>4200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>12100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>4500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>3100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>2100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>1400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>3500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F27" s="3">
         <v>4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>3000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>6700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>5400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>5100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>8700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>3600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>4200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>12100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>3100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>2100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>1400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>3500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2550,8 +2665,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2594,56 +2715,62 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-600</v>
       </c>
-      <c r="Y29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>3000</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>3000</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2734,8 +2861,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2826,8 +2959,14 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2841,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -2856,13 +2995,13 @@
         <v>-100</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2895,123 +3034,135 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-13100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F33" s="3">
         <v>4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>6700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>5400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>5100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>10200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>8700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>3600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>12100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>7500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>3100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>2100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>1400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>3500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3102,197 +3253,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F35" s="3">
         <v>4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>6700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>5400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>5100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>10200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>8700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>3600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>12100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>7500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>3100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>2100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>1400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>3500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44751</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44639</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44555</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44387</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44275</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44191</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44107</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44023</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43911</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43743</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43659</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43547</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43379</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43295</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43183</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43015</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42931</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42819</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3325,8 +3494,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3359,100 +3530,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>6800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>16700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>5900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>5200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>2800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>11100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>15600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>1600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>1600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>2300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>2500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3543,376 +3722,406 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>50100</v>
+      </c>
+      <c r="F43" s="3">
         <v>65500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>56500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>50600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>57400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>66300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>60600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>67300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>66700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>68800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>52200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>54500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>65300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>63800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>49500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>32600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>35600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>37200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>36900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>33000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>41800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>36500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>30800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>29400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>40100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>35300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>33000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>29300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>36700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>96000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>92500</v>
+      </c>
+      <c r="F44" s="3">
         <v>105300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>111700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>122500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>121900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>135000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>130200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>114600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>92400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>91800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>86600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>91400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>72500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>63700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>41700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>42200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>42300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>48400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>48000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>47700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>39100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>45700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>41500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>40100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>35200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>42400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>37500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>37200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>33800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G45" s="3">
         <v>3900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>7300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>12700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>7600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>6500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>4800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>4000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>4100</v>
-      </c>
-      <c r="P45" s="3">
-        <v>2600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>2100</v>
       </c>
       <c r="R45" s="3">
         <v>2600</v>
       </c>
       <c r="S45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>2700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>3000</v>
-      </c>
-      <c r="V45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="W45" s="3">
-        <v>4200</v>
       </c>
       <c r="X45" s="3">
         <v>3000</v>
       </c>
       <c r="Y45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA45" s="3">
         <v>2900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>2900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>3400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>3500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>3000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>2900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>4100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>151500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>146800</v>
+      </c>
+      <c r="F46" s="3">
         <v>175900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>172700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>184000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>188200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>209400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>204300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>201000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>171100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>173600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>154300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>155800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>145400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>136900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>109900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>83600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>86900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>93600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>92500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>88000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>87900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>96300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>90600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>75200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>80300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>82800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>75800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>71900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>75600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3983,212 +4192,230 @@
         <v>0</v>
       </c>
       <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
         <v>20200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>20300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>19600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>18500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>17400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>19000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>32200</v>
+      </c>
+      <c r="F48" s="3">
         <v>32600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>32900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>33500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>33900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>36700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>37700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>30700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>27100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>26500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>22900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>21100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>19800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>17300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>16100</v>
-      </c>
-      <c r="R48" s="3">
-        <v>16400</v>
-      </c>
-      <c r="S48" s="3">
-        <v>16200</v>
       </c>
       <c r="T48" s="3">
         <v>16400</v>
       </c>
       <c r="U48" s="3">
-        <v>16700</v>
+        <v>16200</v>
       </c>
       <c r="V48" s="3">
         <v>16400</v>
       </c>
       <c r="W48" s="3">
+        <v>16700</v>
+      </c>
+      <c r="X48" s="3">
+        <v>16400</v>
+      </c>
+      <c r="Y48" s="3">
         <v>15500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>13400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>13000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>13900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>14300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>14200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>13900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>13500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>13700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>13700</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>71000</v>
+      </c>
+      <c r="F49" s="3">
         <v>71600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>72200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>72800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>73400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>73900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>74600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>75000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>53500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>53900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>54300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>54900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>55300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>44500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>44800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>45300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>45600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>45900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>46300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>45800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>46200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>40200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>40500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>40900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>41200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>41600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>42000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>42500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>42300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4279,8 +4506,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4371,37 +4604,43 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3200</v>
+        <v>2900</v>
       </c>
       <c r="E52" s="3">
-        <v>3300</v>
+        <v>3000</v>
       </c>
       <c r="F52" s="3">
         <v>3200</v>
       </c>
       <c r="G52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="H52" s="3">
         <v>3200</v>
       </c>
-      <c r="H52" s="3">
-        <v>300</v>
-      </c>
       <c r="I52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="J52" s="3">
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -4413,13 +4652,13 @@
         <v>100</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S52" s="3">
         <v>100</v>
@@ -4434,10 +4673,10 @@
         <v>100</v>
       </c>
       <c r="W52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
@@ -4449,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="AB52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="3">
         <v>100</v>
@@ -4461,10 +4700,16 @@
         <v>100</v>
       </c>
       <c r="AF52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4555,100 +4800,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>256300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>253000</v>
+      </c>
+      <c r="F54" s="3">
         <v>283400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>281100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>293600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>298700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>320300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>316900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>307100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>251800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>254200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>231600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>232000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>220700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>198700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>170900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>145400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>148800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>156000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>155500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>150300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>149500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>149800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>144100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>150200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>156100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>158200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>150200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>145300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>150800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4681,8 +4938,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4715,100 +4974,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F57" s="3">
         <v>24100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>14700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>17200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>22700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>24700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>27400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>15800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>25100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>14700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>22700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>20900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>32100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>18100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>7800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>9900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>7200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>7800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>9500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>6900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>5200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>4300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>9900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>8000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>6600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>4400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4842,15 +5109,15 @@
       <c r="M58" s="3">
         <v>7100</v>
       </c>
-      <c r="N58" s="3" t="s">
+      <c r="N58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4858,19 +5125,19 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U58" s="3">
         <v>100</v>
       </c>
       <c r="V58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4879,13 +5146,13 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AB58" s="3">
-        <v>1300</v>
       </c>
       <c r="AC58" s="3">
         <v>1300</v>
@@ -4897,239 +5164,257 @@
         <v>1300</v>
       </c>
       <c r="AF58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>16300</v>
+      </c>
+      <c r="F59" s="3">
         <v>13000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>10900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>11500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>22400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>19900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>21200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>21600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>25200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>19200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>16600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>15000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>25100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>21100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>15600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>10300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>9500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>8400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>7100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>11100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>11000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>9700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>8100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>14000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>10800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>9200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>7200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>12800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>33300</v>
+      </c>
+      <c r="F60" s="3">
         <v>44200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>32700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>35900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>38900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>49700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>53000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>56100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>48200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>51400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>38400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>37700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>46100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>53200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>33700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>15500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>18200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>19600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>15700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>14900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>16700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>20400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>16600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>32300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>19500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>22000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>18600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>15100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>18400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>43800</v>
+      </c>
+      <c r="F61" s="3">
         <v>64900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>76800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>88100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>87700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>99600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>94000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>92900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>50400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>51900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>42900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>46900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>30100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -5137,114 +5422,120 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>5200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>7400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>3700</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>3800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>21900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>24700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>22400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>23000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>24200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>11400</v>
+      </c>
+      <c r="F62" s="3">
         <v>13100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>13100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>13300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>13600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>13800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>13900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>6500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>6100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>5500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>5400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>4500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>4600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>5100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>4500</v>
-      </c>
-      <c r="X62" s="3">
-        <v>3000</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>3000</v>
       </c>
       <c r="Z62" s="3">
         <v>3000</v>
@@ -5253,22 +5544,28 @@
         <v>3000</v>
       </c>
       <c r="AB62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AD62" s="3">
         <v>5400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>5200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>5000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>6400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5359,8 +5656,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5451,8 +5754,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5543,100 +5852,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>88400</v>
+      </c>
+      <c r="F66" s="3">
         <v>122200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>122700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>137300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>140200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>163000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>160900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>155400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>105200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>109400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>86500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>90100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>81500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>57700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>38300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>20300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>22600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>29900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>28300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>23300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>21200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>23400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>19600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>39000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>44400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>52100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>46200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>43100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>49000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5669,8 +5990,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5761,8 +6084,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5853,8 +6182,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5945,8 +6280,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6037,100 +6378,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>159800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>160100</v>
+      </c>
+      <c r="F72" s="3">
         <v>147400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>144700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>142600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>144900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>143700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>142400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>138000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>133100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>131200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>131400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>128000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>125200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>126900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>118400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>111100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>112000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>111800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>112800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>112500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>113900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>112000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>110100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>99500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>99900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>94000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>92400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>91600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>91700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6221,8 +6574,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6313,8 +6672,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6405,100 +6770,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>164700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>164600</v>
+      </c>
+      <c r="F76" s="3">
         <v>161200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>158400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>156300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>158500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>157300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>156000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>151600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>146600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>144700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>145100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>141900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>139200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>141000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>132600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>125200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>126200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>126100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>127200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>127000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>128300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>126400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>124600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>111200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>111700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>106100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>104100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>102200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>101700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6589,197 +6966,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44751</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44639</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44555</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44387</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44275</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44191</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44107</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44023</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43911</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43743</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43659</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43547</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43379</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43295</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43183</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43015</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42931</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42819</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F81" s="3">
         <v>4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>6700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>5400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>5100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>10200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>8700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>3600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>12100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>7500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>3100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>2100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>1400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>3500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6812,8 +7207,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6821,91 +7218,97 @@
         <v>1400</v>
       </c>
       <c r="E83" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F83" s="3">
         <v>1400</v>
       </c>
       <c r="G83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I83" s="3">
         <v>900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>2100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>1000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>1300</v>
-      </c>
-      <c r="V83" s="3">
-        <v>900</v>
-      </c>
-      <c r="W83" s="3">
-        <v>800</v>
       </c>
       <c r="X83" s="3">
         <v>900</v>
       </c>
       <c r="Y83" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="Z83" s="3">
         <v>900</v>
       </c>
       <c r="AA83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC83" s="3">
         <v>700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>1000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>1300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6996,8 +7399,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7088,8 +7497,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7180,8 +7595,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7272,8 +7693,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7364,100 +7791,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F89" s="3">
         <v>14800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>8400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>4500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>14300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>4000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>9700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-10200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-8200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>12900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>3900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>8900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>7000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>3000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>4900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>3000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>5900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>10300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7490,100 +7929,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-2800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7674,8 +8121,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7766,100 +8219,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="E94" s="3">
         <v>-400</v>
       </c>
       <c r="F94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-35300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-1400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-4000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-1400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-17800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-500</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-300</v>
       </c>
       <c r="T94" s="3">
         <v>-500</v>
       </c>
       <c r="U94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="V94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W94" s="3">
         <v>-1500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-8000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>34100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7892,8 +8357,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7901,16 +8368,16 @@
         <v>-2100</v>
       </c>
       <c r="E96" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
         <v>-2100</v>
       </c>
       <c r="G96" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="H96" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="I96" s="3">
         <v>-2000</v>
@@ -7919,28 +8386,28 @@
         <v>-2000</v>
       </c>
       <c r="K96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="L96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="M96" s="3">
         <v>-1900</v>
       </c>
       <c r="N96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="O96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="P96" s="3">
         <v>-2000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="R96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="S96" s="3">
         <v>-1800</v>
@@ -7967,10 +8434,10 @@
         <v>-1800</v>
       </c>
       <c r="AA96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AB96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AC96" s="3">
         <v>-1700</v>
@@ -7979,13 +8446,19 @@
         <v>-1700</v>
       </c>
       <c r="AE96" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8076,8 +8549,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8168,8 +8647,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8260,100 +8745,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-14000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-13500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-14000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>3500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>40200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-4700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-2200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>14000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>22800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-3100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-7900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-5900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>1900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-24300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8444,8 +8941,14 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8453,87 +8956,93 @@
         <v>300</v>
       </c>
       <c r="E102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F102" s="3">
+        <v>300</v>
+      </c>
+      <c r="G102" s="3">
         <v>-5500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-4100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>4800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>10500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>1500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-8300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>12700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,448 +656,461 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44751</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44639</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44387</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44275</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44191</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44107</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44023</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43911</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43743</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43659</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43547</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43379</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43295</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43183</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43015</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42931</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42819</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E8" s="3">
         <v>57300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>65500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>73400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>56900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>72100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>74900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>94300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>72400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>81300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>99700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>59200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>74800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>78100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>83500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>37300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>47000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>45800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>55600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>32100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>51000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>44000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>48700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>52200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>41900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>53900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>31900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>49800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E9" s="3">
         <v>43000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>55200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>51100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>45900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>56000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>70600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>52300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>57100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>63000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>74600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>41800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>56900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>54500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>60300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>36200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>35700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>42700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>23600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>38800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>31600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>37200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>40200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>30500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>40800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>39600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E10" s="3">
         <v>14400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>18200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>20100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>16300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>25100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>17400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>10200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>12900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>8500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>12400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>11500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>10200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1132,8 +1145,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1230,8 +1244,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1328,8 +1345,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1418,16 +1438,19 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-300</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1447,40 +1470,40 @@
         <v>600</v>
       </c>
       <c r="I15" s="3">
+        <v>600</v>
+      </c>
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>600</v>
-      </c>
-      <c r="M15" s="3">
-        <v>400</v>
       </c>
       <c r="N15" s="3">
         <v>400</v>
       </c>
       <c r="O15" s="3">
+        <v>400</v>
+      </c>
+      <c r="P15" s="3">
         <v>600</v>
-      </c>
-      <c r="P15" s="3">
-        <v>400</v>
       </c>
       <c r="Q15" s="3">
         <v>400</v>
       </c>
       <c r="R15" s="3">
+        <v>400</v>
+      </c>
+      <c r="S15" s="3">
         <v>300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>400</v>
-      </c>
-      <c r="T15" s="3">
-        <v>300</v>
       </c>
       <c r="U15" s="3">
         <v>300</v>
@@ -1489,10 +1512,10 @@
         <v>300</v>
       </c>
       <c r="W15" s="3">
+        <v>300</v>
+      </c>
+      <c r="X15" s="3">
         <v>500</v>
-      </c>
-      <c r="X15" s="3">
-        <v>300</v>
       </c>
       <c r="Y15" s="3">
         <v>300</v>
@@ -1501,22 +1524,22 @@
         <v>300</v>
       </c>
       <c r="AA15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB15" s="3">
         <v>400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>300</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>400</v>
       </c>
       <c r="AD15" s="3">
         <v>400</v>
       </c>
       <c r="AE15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF15" s="3">
         <v>500</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>400</v>
       </c>
       <c r="AG15" s="3">
         <v>400</v>
@@ -1524,8 +1547,11 @@
       <c r="AH15" s="3">
         <v>400</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1557,204 +1583,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E17" s="3">
         <v>54200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>60500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>66900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>61500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>56800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>67300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>70700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>86100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>67000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>73600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>89000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>67800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>65300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>72700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>34900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>43500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>53200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>31700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>46000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>38800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>46700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>30400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>47100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>37800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>50600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>29600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>46100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>3100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1789,8 +1822,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1810,25 +1844,25 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1864,129 +1898,135 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>13100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E21" s="3">
         <v>4400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>5800</v>
       </c>
       <c r="J21" s="3">
         <v>5800</v>
       </c>
       <c r="K21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L21" s="3">
         <v>10300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>10500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>13900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>4300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>16200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1994,55 +2034,55 @@
         <v>700</v>
       </c>
       <c r="E22" s="3">
+        <v>700</v>
+      </c>
+      <c r="F22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>500</v>
-      </c>
-      <c r="N22" s="3">
-        <v>400</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
       </c>
       <c r="P22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V22" s="3">
         <v>100</v>
@@ -2054,13 +2094,13 @@
         <v>100</v>
       </c>
       <c r="Y22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
       <c r="AA22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>200</v>
@@ -2083,204 +2123,213 @@
       <c r="AH22" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10300</v>
-      </c>
-      <c r="P23" s="3">
-        <v>6900</v>
       </c>
       <c r="Q23" s="3">
         <v>6900</v>
       </c>
       <c r="R23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S23" s="3">
         <v>12800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>14900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2377,204 +2426,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2671,8 +2729,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2721,17 +2782,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2739,23 +2800,23 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>3000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2763,14 +2824,17 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2867,8 +2931,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2965,8 +3032,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2986,25 +3056,25 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3040,129 +3110,135 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>1800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>300</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>3600</v>
       </c>
       <c r="Z33" s="3">
         <v>3600</v>
       </c>
       <c r="AA33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AB33" s="3">
         <v>12100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3259,209 +3335,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>1800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>300</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>3600</v>
       </c>
       <c r="Z35" s="3">
         <v>3600</v>
       </c>
       <c r="AA35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AB35" s="3">
         <v>12100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44751</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44639</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44387</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44275</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44191</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44107</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44023</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43911</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43743</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43659</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43547</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43379</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43295</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43183</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43015</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42931</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42819</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3496,8 +3581,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3532,106 +3618,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>400</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
-        <v>0</v>
-      </c>
       <c r="F41" s="3">
+        <v>0</v>
+      </c>
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6100</v>
-      </c>
-      <c r="I41" s="3">
-        <v>4000</v>
       </c>
       <c r="J41" s="3">
         <v>4000</v>
       </c>
       <c r="K41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L41" s="3">
         <v>6200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>16700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2900</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>1600</v>
       </c>
       <c r="AD41" s="3">
         <v>1600</v>
       </c>
       <c r="AE41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AF41" s="3">
         <v>2300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3728,400 +3818,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E43" s="3">
         <v>52300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>50100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>65500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>50600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>66300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>60600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>67300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>66700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>68800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>52200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>54500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>65300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>63800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>49500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>32600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>35600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>37200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>36900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>33000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>41800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>36500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>30800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>29400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>40100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>35300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>33000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>29300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>36700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E44" s="3">
         <v>96000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>92500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>105300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>111700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>122500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>121900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>135000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>130200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>114600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>92400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>91800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>86600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>91400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>72500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>63700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>41700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>42200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>42300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>48400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>48000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>47700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>39100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>45700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>41500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>40100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>35200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>42400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>37500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>37200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>33800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="3">
         <v>2900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4300</v>
       </c>
       <c r="F45" s="3">
         <v>4300</v>
       </c>
       <c r="G45" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H45" s="3">
         <v>3900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>4900</v>
       </c>
       <c r="I45" s="3">
         <v>4900</v>
       </c>
       <c r="J45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K45" s="3">
         <v>4100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2700</v>
-      </c>
-      <c r="W45" s="3">
-        <v>3000</v>
       </c>
       <c r="X45" s="3">
         <v>3000</v>
       </c>
       <c r="Y45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="Z45" s="3">
         <v>4200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3000</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>2900</v>
       </c>
       <c r="AB45" s="3">
         <v>2900</v>
       </c>
       <c r="AC45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AD45" s="3">
         <v>3400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>139100</v>
+      </c>
+      <c r="E46" s="3">
         <v>151500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>146800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>175900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>172700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>184000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>188200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>209400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>204300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>201000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>171100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>173600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>154300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>155800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>145400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>136900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>109900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>83600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>86900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>93600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>92500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>88000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>87900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>96300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>90600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>75200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>80300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>82800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>75800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>71900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>75600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4198,224 +4303,233 @@
         <v>0</v>
       </c>
       <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>20200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>20300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>19600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>18500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>17400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>19000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E48" s="3">
         <v>31500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>19800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>17300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>15500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>14300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13500</v>
-      </c>
-      <c r="AG48" s="3">
-        <v>13700</v>
       </c>
       <c r="AH48" s="3">
         <v>13700</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>13700</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>69800</v>
+      </c>
+      <c r="E49" s="3">
         <v>70400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>71000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>71600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>72200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>73400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>75000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>53500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>53900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>54300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>54900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>55300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>44500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>44800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>45300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>45600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>45900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>46300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>45800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>46200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>40200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>40500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>40900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>41200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>41600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>42000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>42500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>42300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4512,8 +4626,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4610,8 +4727,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4619,22 +4739,22 @@
         <v>2900</v>
       </c>
       <c r="E52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F52" s="3">
         <v>3000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3200</v>
       </c>
       <c r="I52" s="3">
         <v>3200</v>
       </c>
       <c r="J52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="K52" s="3">
         <v>300</v>
@@ -4643,7 +4763,7 @@
         <v>300</v>
       </c>
       <c r="M52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -4658,10 +4778,10 @@
         <v>100</v>
       </c>
       <c r="R52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -4679,7 +4799,7 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -4694,7 +4814,7 @@
         <v>0</v>
       </c>
       <c r="AD52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="3">
         <v>100</v>
@@ -4706,10 +4826,13 @@
         <v>100</v>
       </c>
       <c r="AH52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4806,106 +4929,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>243100</v>
+      </c>
+      <c r="E54" s="3">
         <v>256300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>253000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>283400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>281100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>293600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>298700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>320300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>316900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>307100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>251800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>254200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>231600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>232000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>220700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>198700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>170900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>145400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>148800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>156000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>155500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>150300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>149500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>149800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>144100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>150200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>156100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>158200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>150200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>145300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>150800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4940,8 +5069,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4976,106 +5106,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E57" s="3">
         <v>16000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>24700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>25100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>14700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>32100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5115,12 +5249,12 @@
       <c r="O58" s="3">
         <v>7100</v>
       </c>
-      <c r="P58" s="3" t="s">
+      <c r="P58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5131,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V58" s="3">
         <v>100</v>
@@ -5140,7 +5274,7 @@
         <v>100</v>
       </c>
       <c r="X58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5152,10 +5286,10 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>1300</v>
       </c>
       <c r="AD58" s="3">
         <v>1300</v>
@@ -5170,254 +5304,263 @@
         <v>1300</v>
       </c>
       <c r="AH58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E59" s="3">
         <v>11000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>25100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>10300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>8400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>7100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>8100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>7200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E60" s="3">
         <v>34100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>33300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>35900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>38900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>49700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>53000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>56100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>48200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>51400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>37700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>46100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>53200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>33700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>15500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>18200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>19600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>20400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>32300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>22000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>18600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E61" s="3">
         <v>46400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>43800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>64900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>76800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>88100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>87700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>99600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>94000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>92900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>51900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>46900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>30100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -5428,17 +5571,17 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>5200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3700</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5446,99 +5589,102 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>3800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>21900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>24700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>22400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>23000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E62" s="3">
         <v>11100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>13100</v>
       </c>
       <c r="G62" s="3">
         <v>13100</v>
       </c>
       <c r="H62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I62" s="3">
         <v>13300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4400</v>
-      </c>
-      <c r="V62" s="3">
-        <v>5100</v>
       </c>
       <c r="W62" s="3">
         <v>5100</v>
       </c>
       <c r="X62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Y62" s="3">
         <v>4800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4500</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>3000</v>
       </c>
       <c r="AA62" s="3">
         <v>3000</v>
@@ -5550,22 +5696,25 @@
         <v>3000</v>
       </c>
       <c r="AD62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE62" s="3">
         <v>5400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>5200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5662,8 +5811,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5760,8 +5912,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5858,106 +6013,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E66" s="3">
         <v>91600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>88400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>122200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>122700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>137300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>140200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>163000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>160900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>155400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>105200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>109400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>86500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>81500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>57700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>20300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>22600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>29900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>23300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>21200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>19600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>39000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>44400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>52100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>46200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>43100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>49000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5992,8 +6153,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6090,8 +6252,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6188,8 +6353,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6286,8 +6454,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6384,106 +6555,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>160600</v>
+      </c>
+      <c r="E72" s="3">
         <v>159800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>160100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>147400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>144700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>142600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>144900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>143700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>142400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>138000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>133100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>131200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>131400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>128000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>125200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>126900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>118400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>111100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>112000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>111800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>112800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>112500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>113900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>112000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>110100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>99500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>99900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>94000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>92400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>91600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>91700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6580,8 +6757,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6678,8 +6858,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6776,106 +6959,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E76" s="3">
         <v>164700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>164600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>161200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>158400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>156300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>158500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>157300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>156000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>151600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>146600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>144700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>145100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>141900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>139200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>141000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>132600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>125200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>126200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>126100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>127200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>127000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>128300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>126400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>124600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>111200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>111700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>106100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>104100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>102200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>101700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6972,209 +7161,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44751</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44639</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44387</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44275</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44191</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44107</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44023</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43911</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43743</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43659</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43547</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43379</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43295</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43183</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43015</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42931</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42819</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>1800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>300</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>3600</v>
       </c>
       <c r="Z81" s="3">
         <v>3600</v>
       </c>
       <c r="AA81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AB81" s="3">
         <v>12100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7209,8 +7407,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7218,10 +7417,10 @@
         <v>1400</v>
       </c>
       <c r="E83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1400</v>
       </c>
       <c r="G83" s="3">
         <v>1400</v>
@@ -7230,85 +7429,88 @@
         <v>1400</v>
       </c>
       <c r="I83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J83" s="3">
         <v>900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7405,8 +7607,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7503,8 +7708,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7601,8 +7809,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7699,8 +7910,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7797,106 +8011,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>13300</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>20600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>14800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>8900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>7000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>5900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7931,106 +8151,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-500</v>
       </c>
       <c r="F91" s="3">
         <v>-500</v>
       </c>
       <c r="G91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
       </c>
       <c r="J91" s="3">
         <v>-300</v>
       </c>
       <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-1000</v>
       </c>
       <c r="Z91" s="3">
         <v>-1000</v>
       </c>
       <c r="AA91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-400</v>
       </c>
       <c r="AH91" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8127,8 +8351,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8225,106 +8452,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-17800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>34100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8359,8 +8592,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8368,10 +8602,10 @@
         <v>-2100</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-2100</v>
       </c>
       <c r="F96" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
         <v>-2100</v>
@@ -8380,7 +8614,7 @@
         <v>-2100</v>
       </c>
       <c r="I96" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="J96" s="3">
         <v>-2000</v>
@@ -8392,7 +8626,7 @@
         <v>-2000</v>
       </c>
       <c r="M96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="N96" s="3">
         <v>-1900</v>
@@ -8401,7 +8635,7 @@
         <v>-1900</v>
       </c>
       <c r="P96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="Q96" s="3">
         <v>-2000</v>
@@ -8410,7 +8644,7 @@
         <v>-2000</v>
       </c>
       <c r="S96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="T96" s="3">
         <v>-1800</v>
@@ -8440,7 +8674,7 @@
         <v>-1800</v>
       </c>
       <c r="AC96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AD96" s="3">
         <v>-1700</v>
@@ -8452,13 +8686,16 @@
         <v>-1700</v>
       </c>
       <c r="AG96" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AH96" s="3">
         <v>-1600</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-1600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8555,8 +8792,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8653,8 +8893,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8751,106 +8994,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E100" s="3">
         <v>600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-21100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>40200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>14000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>22800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-3100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-7900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5900</v>
-      </c>
-      <c r="W100" s="3">
-        <v>1900</v>
       </c>
       <c r="X100" s="3">
         <v>1900</v>
       </c>
       <c r="Y100" s="3">
-        <v>-1800</v>
+        <v>1900</v>
       </c>
       <c r="Z100" s="3">
         <v>-1800</v>
       </c>
       <c r="AA100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8947,102 +9196,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2100</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>10500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,461 +656,474 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44751</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44387</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44275</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44191</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44107</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44023</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43911</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43743</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43659</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43547</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43379</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43295</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43183</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43015</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42931</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42819</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>67700</v>
+      </c>
+      <c r="E8" s="3">
         <v>62500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>57300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>65500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>73400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>67800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>56900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>72100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>74900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>94300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>72400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>73400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>81300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>99700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>59200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>74800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>78100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>83500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>37300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>47000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>45800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>55600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>32100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>51000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>44000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>48700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>32100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>52200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>41900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>53900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>31900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>49800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E9" s="3">
         <v>47400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>55200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>51100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>56000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>61300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>70600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>52300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>57100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>63000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>74600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>41800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>56900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>54500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>60300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>36200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>35700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>42700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>23600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>38800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>31600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>37200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>23200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>40200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>30500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>40800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>23600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>39600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E10" s="3">
         <v>15100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15900</v>
       </c>
-      <c r="G10" s="3">
-        <v>18200</v>
-      </c>
       <c r="H10" s="3">
-        <v>16700</v>
+        <v>18100</v>
       </c>
       <c r="I10" s="3">
-        <v>11000</v>
+        <v>16600</v>
       </c>
       <c r="J10" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K10" s="3">
         <v>16100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>20100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>25100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>17400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>10200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>12900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>12200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>11500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>12000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>8300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>10200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1146,8 +1159,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1160,8 +1174,8 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
+      <c r="G12" s="3">
+        <v>3100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>8</v>
@@ -1247,8 +1261,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1348,31 +1365,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-3900</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1441,21 +1461,24 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-300</v>
-      </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="E15" s="3">
         <v>600</v>
@@ -1473,40 +1496,40 @@
         <v>600</v>
       </c>
       <c r="J15" s="3">
+        <v>600</v>
+      </c>
+      <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>600</v>
-      </c>
-      <c r="N15" s="3">
-        <v>400</v>
       </c>
       <c r="O15" s="3">
         <v>400</v>
       </c>
       <c r="P15" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q15" s="3">
         <v>600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>400</v>
       </c>
       <c r="R15" s="3">
         <v>400</v>
       </c>
       <c r="S15" s="3">
+        <v>400</v>
+      </c>
+      <c r="T15" s="3">
         <v>300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>400</v>
-      </c>
-      <c r="U15" s="3">
-        <v>300</v>
       </c>
       <c r="V15" s="3">
         <v>300</v>
@@ -1515,10 +1538,10 @@
         <v>300</v>
       </c>
       <c r="X15" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y15" s="3">
         <v>500</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>300</v>
       </c>
       <c r="Z15" s="3">
         <v>300</v>
@@ -1527,22 +1550,22 @@
         <v>300</v>
       </c>
       <c r="AB15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC15" s="3">
         <v>400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>300</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>400</v>
       </c>
       <c r="AE15" s="3">
         <v>400</v>
       </c>
       <c r="AF15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG15" s="3">
         <v>500</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>400</v>
       </c>
       <c r="AH15" s="3">
         <v>400</v>
@@ -1550,8 +1573,11 @@
       <c r="AI15" s="3">
         <v>400</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1584,210 +1610,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>63700</v>
+      </c>
+      <c r="E17" s="3">
         <v>58100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>54200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>60500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>66900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>61500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>56800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>67300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>70700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>86100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>63400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>67000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>73600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>89000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>67800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>65300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>72700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>34900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>43500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>42900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>53200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>31700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>46000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>38800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>46700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>30400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>47100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>37800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>50600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>29600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>46100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4400</v>
+        <v>4100</v>
       </c>
       <c r="E18" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F18" s="3">
         <v>3100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5000</v>
       </c>
-      <c r="G18" s="3">
-        <v>6500</v>
-      </c>
       <c r="H18" s="3">
+        <v>6400</v>
+      </c>
+      <c r="I18" s="3">
         <v>6300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>9000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1823,8 +1856,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1847,25 +1881,25 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1901,191 +1935,197 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>13100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>600</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5800</v>
+        <v>5100</v>
       </c>
       <c r="E21" s="3">
-        <v>4400</v>
+        <v>5100</v>
       </c>
       <c r="F21" s="3">
-        <v>6400</v>
+        <v>3700</v>
       </c>
       <c r="G21" s="3">
-        <v>7900</v>
+        <v>5600</v>
       </c>
       <c r="H21" s="3">
-        <v>7700</v>
+        <v>7100</v>
       </c>
       <c r="I21" s="3">
-        <v>1600</v>
+        <v>6900</v>
       </c>
       <c r="J21" s="3">
-        <v>5800</v>
+        <v>800</v>
       </c>
       <c r="K21" s="3">
         <v>5800</v>
       </c>
       <c r="L21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="M21" s="3">
         <v>10300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>10500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>12300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>13900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>4300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>16200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>2600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E22" s="3">
         <v>700</v>
       </c>
       <c r="F22" s="3">
+        <v>700</v>
+      </c>
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
       </c>
       <c r="P22" s="3">
         <v>400</v>
       </c>
       <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>100</v>
@@ -2097,13 +2137,13 @@
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
       <c r="AB22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="3">
         <v>200</v>
@@ -2126,210 +2166,219 @@
       <c r="AI22" s="3">
         <v>200</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E23" s="3">
         <v>3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10300</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>6900</v>
       </c>
       <c r="R23" s="3">
         <v>6900</v>
       </c>
       <c r="S23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="T23" s="3">
         <v>12800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2429,210 +2478,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E26" s="3">
         <v>2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E27" s="3">
         <v>2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2732,8 +2790,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2785,17 +2846,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2803,23 +2864,23 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>3000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2827,14 +2888,17 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2934,8 +2998,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3035,8 +3102,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3059,25 +3129,25 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3113,132 +3183,138 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-600</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E33" s="3">
         <v>2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>300</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>3600</v>
       </c>
       <c r="AA33" s="3">
         <v>3600</v>
       </c>
       <c r="AB33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AC33" s="3">
         <v>12100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3338,215 +3414,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E35" s="3">
         <v>2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>300</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>3600</v>
       </c>
       <c r="AA35" s="3">
         <v>3600</v>
       </c>
       <c r="AB35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AC35" s="3">
         <v>12100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44751</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44387</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44275</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44191</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44107</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44023</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43911</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43743</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43659</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43547</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43379</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43295</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43183</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43015</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42931</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42819</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3582,8 +3667,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3619,8 +3705,9 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3628,100 +3715,103 @@
         <v>400</v>
       </c>
       <c r="E41" s="3">
+        <v>400</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
       <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
         <v>900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>4000</v>
       </c>
       <c r="K41" s="3">
         <v>4000</v>
       </c>
       <c r="L41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M41" s="3">
         <v>6200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>16700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>15600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2900</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>1600</v>
       </c>
       <c r="AE41" s="3">
         <v>1600</v>
       </c>
       <c r="AF41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AG41" s="3">
         <v>2300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3821,435 +3911,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>49700</v>
+        <v>53500</v>
       </c>
       <c r="E43" s="3">
+        <v>47800</v>
+      </c>
+      <c r="F43" s="3">
         <v>52300</v>
       </c>
-      <c r="F43" s="3">
-        <v>50100</v>
-      </c>
       <c r="G43" s="3">
-        <v>65500</v>
+        <v>50000</v>
       </c>
       <c r="H43" s="3">
-        <v>56500</v>
+        <v>63400</v>
       </c>
       <c r="I43" s="3">
-        <v>50600</v>
+        <v>55000</v>
       </c>
       <c r="J43" s="3">
+        <v>50500</v>
+      </c>
+      <c r="K43" s="3">
         <v>57400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>66300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>60600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>67300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>68800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>52200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>54500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>65300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>63800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>49500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>32600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>35600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>37200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>36900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>33000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>41800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>36500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>30800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>29400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>40100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>35300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>33000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>29300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>36700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E44" s="3">
         <v>86600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>96000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>92500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>105300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>111700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>122500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>121900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>135000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>130200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>114600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>92400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>91800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>86600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>91400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>72500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>63700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>41700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>42200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>42300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>48400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>48000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>47700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>39100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>45700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>41500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>40100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>35200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>42400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>37500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>37200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>33800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>4300</v>
+        <v>1800</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>4300</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>3900</v>
+        <v>2100</v>
       </c>
       <c r="I45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>200</v>
+      </c>
+      <c r="K45" s="3">
         <v>4900</v>
       </c>
-      <c r="J45" s="3">
-        <v>4900</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2700</v>
-      </c>
-      <c r="X45" s="3">
-        <v>3000</v>
       </c>
       <c r="Y45" s="3">
         <v>3000</v>
       </c>
       <c r="Z45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AA45" s="3">
         <v>4200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3000</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>2900</v>
       </c>
       <c r="AC45" s="3">
         <v>2900</v>
       </c>
       <c r="AD45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE45" s="3">
         <v>3400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E46" s="3">
         <v>139100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>151500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>146800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>175900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>172700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>184000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>188200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>209400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>204300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>201000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>171100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>173600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>154300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>155800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>145400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>136900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>109900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>83600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>86900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>93600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>92500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>88000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>87900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>96300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>90600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>75200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>80300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>82800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>75800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>71900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>75600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4306,230 +4411,239 @@
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>20200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>20300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>19600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>18500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>17400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>19000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E48" s="3">
         <v>31300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>30700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>21100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>17300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>15500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>14300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13500</v>
-      </c>
-      <c r="AH48" s="3">
-        <v>13700</v>
       </c>
       <c r="AI48" s="3">
         <v>13700</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>13700</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68700</v>
+      </c>
+      <c r="E49" s="3">
         <v>69800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>70400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>71000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>72800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>73400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>73900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>74600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>75000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>53500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>53900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>54300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>54900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>55300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>44500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>44800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>45300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>45600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>45900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>46300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>45800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>46200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>40200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>40500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>40900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>41200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>41600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>42000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>42500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>42300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4629,8 +4743,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4730,34 +4847,37 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2900</v>
+        <v>1000</v>
       </c>
       <c r="E52" s="3">
         <v>2900</v>
       </c>
       <c r="F52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G52" s="3">
         <v>3000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>3200</v>
       </c>
       <c r="J52" s="3">
         <v>3200</v>
       </c>
       <c r="K52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="L52" s="3">
         <v>300</v>
@@ -4766,7 +4886,7 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
@@ -4781,10 +4901,10 @@
         <v>100</v>
       </c>
       <c r="S52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -4802,7 +4922,7 @@
         <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
@@ -4817,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="AE52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF52" s="3">
         <v>100</v>
@@ -4829,10 +4949,13 @@
         <v>100</v>
       </c>
       <c r="AI52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4932,109 +5055,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>244900</v>
+      </c>
+      <c r="E54" s="3">
         <v>243100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>256300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>253000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>283400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>281100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>293600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>298700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>320300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>316900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>307100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>251800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>254200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>231600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>232000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>220700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>198700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>170900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>145400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>148800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>156000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>155500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>150300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>149500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>149800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>144100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>150200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>156100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>158200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>150200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>145300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>150800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5070,8 +5199,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5107,132 +5237,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E57" s="3">
         <v>12800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>9400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>22700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>14700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>32100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>18100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>6900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7100</v>
+        <v>8200</v>
       </c>
       <c r="E58" s="3">
-        <v>7100</v>
+        <v>8200</v>
       </c>
       <c r="F58" s="3">
-        <v>7100</v>
+        <v>8200</v>
       </c>
       <c r="G58" s="3">
-        <v>7100</v>
+        <v>8200</v>
       </c>
       <c r="H58" s="3">
-        <v>7100</v>
+        <v>8200</v>
       </c>
       <c r="I58" s="3">
-        <v>7100</v>
+        <v>8100</v>
       </c>
       <c r="J58" s="3">
-        <v>7100</v>
+        <v>8100</v>
       </c>
       <c r="K58" s="3">
         <v>7100</v>
@@ -5252,12 +5386,12 @@
       <c r="P58" s="3">
         <v>7100</v>
       </c>
-      <c r="Q58" s="3" t="s">
+      <c r="Q58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
@@ -5268,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W58" s="3">
         <v>100</v>
@@ -5277,7 +5411,7 @@
         <v>100</v>
       </c>
       <c r="Y58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -5289,10 +5423,10 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>1300</v>
       </c>
       <c r="AE58" s="3">
         <v>1300</v>
@@ -5307,263 +5441,272 @@
         <v>1300</v>
       </c>
       <c r="AI58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
+        <v>400</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
+        <v>22400</v>
+      </c>
+      <c r="L59" s="3">
+        <v>19900</v>
+      </c>
+      <c r="M59" s="3">
+        <v>21200</v>
+      </c>
+      <c r="N59" s="3">
+        <v>21600</v>
+      </c>
+      <c r="O59" s="3">
+        <v>25200</v>
+      </c>
+      <c r="P59" s="3">
+        <v>19200</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>16600</v>
+      </c>
+      <c r="R59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="S59" s="3">
+        <v>25100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>21100</v>
+      </c>
+      <c r="U59" s="3">
+        <v>15600</v>
+      </c>
+      <c r="V59" s="3">
+        <v>9100</v>
+      </c>
+      <c r="W59" s="3">
         <v>10300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="X59" s="3">
+        <v>9500</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="Z59" s="3">
+        <v>7100</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>11100</v>
+      </c>
+      <c r="AB59" s="3">
         <v>11000</v>
       </c>
-      <c r="F59" s="3">
-        <v>16300</v>
-      </c>
-      <c r="G59" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>10900</v>
-      </c>
-      <c r="I59" s="3">
-        <v>11500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>22400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>19900</v>
-      </c>
-      <c r="L59" s="3">
-        <v>21200</v>
-      </c>
-      <c r="M59" s="3">
-        <v>21600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>25200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>19200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>16600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>15000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>25100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>21100</v>
-      </c>
-      <c r="T59" s="3">
-        <v>15600</v>
-      </c>
-      <c r="U59" s="3">
-        <v>9100</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="AC59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>8100</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AF59" s="3">
+        <v>10800</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>7200</v>
+      </c>
+      <c r="AI59" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>10300</v>
       </c>
-      <c r="W59" s="3">
-        <v>9500</v>
-      </c>
-      <c r="X59" s="3">
-        <v>8400</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>7100</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>11100</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>11000</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>9700</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>8100</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>14000</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>10800</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AG59" s="3">
-        <v>7200</v>
-      </c>
-      <c r="AH59" s="3">
-        <v>12800</v>
-      </c>
-      <c r="AI59" s="3">
-        <v>10300</v>
-      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E60" s="3">
         <v>30200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>33300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>32700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>35900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>49700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>53000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>56100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>48200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>51400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>37700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>46100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>53200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>33700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>15500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>18200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>15700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>16700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>20400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>32300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>19500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>22000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>18600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>15100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>36000</v>
+        <v>29500</v>
       </c>
       <c r="E61" s="3">
-        <v>46400</v>
+        <v>43400</v>
       </c>
       <c r="F61" s="3">
-        <v>43800</v>
+        <v>54000</v>
       </c>
       <c r="G61" s="3">
-        <v>64900</v>
+        <v>51700</v>
       </c>
       <c r="H61" s="3">
-        <v>76800</v>
+        <v>73100</v>
       </c>
       <c r="I61" s="3">
-        <v>88100</v>
+        <v>85000</v>
       </c>
       <c r="J61" s="3">
+        <v>96500</v>
+      </c>
+      <c r="K61" s="3">
         <v>87700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>99600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>94000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>92900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>51900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>46900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>30100</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -5574,17 +5717,17 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>5200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3700</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5592,102 +5735,105 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>3800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>21900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>24700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>22400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>23000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>24200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>10800</v>
+        <v>300</v>
       </c>
       <c r="E62" s="3">
-        <v>11100</v>
+        <v>300</v>
       </c>
       <c r="F62" s="3">
-        <v>11400</v>
+        <v>400</v>
       </c>
       <c r="G62" s="3">
-        <v>13100</v>
+        <v>400</v>
       </c>
       <c r="H62" s="3">
-        <v>13100</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>13300</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
+        <v>400</v>
+      </c>
+      <c r="K62" s="3">
         <v>13600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4400</v>
-      </c>
-      <c r="W62" s="3">
-        <v>5100</v>
       </c>
       <c r="X62" s="3">
         <v>5100</v>
       </c>
       <c r="Y62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Z62" s="3">
         <v>4800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4500</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>3000</v>
       </c>
       <c r="AB62" s="3">
         <v>3000</v>
@@ -5699,22 +5845,25 @@
         <v>3000</v>
       </c>
       <c r="AE62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AF62" s="3">
         <v>5400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>5200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5814,8 +5963,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5915,8 +6067,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6016,109 +6171,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E66" s="3">
         <v>77100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>88400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>122200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>122700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>137300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>140200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>163000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>160900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>155400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>105200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>109400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>86500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>90100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>81500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>57700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>38300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>20300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>22600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>29900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>23300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>21200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>19600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>39000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>44400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>52100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>46200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>43100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>49000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6154,8 +6315,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6255,8 +6417,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6356,8 +6521,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6457,8 +6625,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6558,109 +6729,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>164200</v>
+      </c>
+      <c r="E72" s="3">
         <v>160600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>159800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>160100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>147400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>144700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>142600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>144900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>143700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>142400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>138000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>133100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>131200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>131400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>128000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>125200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>126900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>118400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>111100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>112000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>111800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>112800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>112500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>113900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>112000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>110100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>99500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>99900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>94000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>92400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>91600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>91700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6760,8 +6937,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6861,8 +7041,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6962,109 +7145,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>170100</v>
+      </c>
+      <c r="E76" s="3">
         <v>166000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>164700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>164600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>161200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>158400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>156300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>158500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>157300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>156000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>151600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>146600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>144700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>145100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>141900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>139200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>141000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>132600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>125200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>126200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>126100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>127200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>127000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>128300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>126400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>124600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>111200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>111700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>106100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>104100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>102200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>101700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7164,215 +7353,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44751</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44387</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44275</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44191</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44107</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44023</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43911</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43743</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43659</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43547</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43379</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43295</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43183</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43015</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42931</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42819</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E81" s="3">
         <v>2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>300</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>3600</v>
       </c>
       <c r="AA81" s="3">
         <v>3600</v>
       </c>
       <c r="AB81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AC81" s="3">
         <v>12100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7408,109 +7606,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="F83" s="3">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="G83" s="3">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="J83" s="3">
         <v>900</v>
       </c>
       <c r="K83" s="3">
+        <v>900</v>
+      </c>
+      <c r="L83" s="3">
         <v>1600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7610,8 +7812,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7711,8 +7916,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7812,8 +8020,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7913,8 +8124,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8014,109 +8228,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E89" s="3">
         <v>13300</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>20600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-10200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-5900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>8900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>7000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>10300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8152,109 +8372,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-500</v>
       </c>
       <c r="G91" s="3">
         <v>-500</v>
       </c>
       <c r="H91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA91" s="3">
         <v>-1000</v>
       </c>
       <c r="AB91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-400</v>
       </c>
       <c r="AI91" s="3">
         <v>-400</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8354,8 +8578,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8455,109 +8682,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-17800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>34100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8593,31 +8826,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2100</v>
+        <v>2100</v>
       </c>
       <c r="E96" s="3">
-        <v>-2100</v>
+        <v>2100</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G96" s="3">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-2100</v>
+        <v>2100</v>
       </c>
       <c r="I96" s="3">
-        <v>-2100</v>
+        <v>2100</v>
       </c>
       <c r="J96" s="3">
-        <v>-2000</v>
+        <v>2100</v>
       </c>
       <c r="K96" s="3">
         <v>-2000</v>
@@ -8629,7 +8863,7 @@
         <v>-2000</v>
       </c>
       <c r="N96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="O96" s="3">
         <v>-1900</v>
@@ -8638,7 +8872,7 @@
         <v>-1900</v>
       </c>
       <c r="Q96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="R96" s="3">
         <v>-2000</v>
@@ -8647,7 +8881,7 @@
         <v>-2000</v>
       </c>
       <c r="T96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="U96" s="3">
         <v>-1800</v>
@@ -8677,7 +8911,7 @@
         <v>-1800</v>
       </c>
       <c r="AD96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AE96" s="3">
         <v>-1700</v>
@@ -8689,13 +8923,16 @@
         <v>-1700</v>
       </c>
       <c r="AH96" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AI96" s="3">
         <v>-1600</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-1600</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8795,8 +9032,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8896,8 +9136,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8997,132 +9240,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>3500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>40200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>22800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-3100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-7900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-5900</v>
-      </c>
-      <c r="X100" s="3">
-        <v>1900</v>
       </c>
       <c r="Y100" s="3">
         <v>1900</v>
       </c>
       <c r="Z100" s="3">
-        <v>-1800</v>
+        <v>1900</v>
       </c>
       <c r="AA100" s="3">
         <v>-1800</v>
       </c>
       <c r="AB100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-24300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9199,8 +9448,11 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9208,96 +9460,99 @@
         <v>100</v>
       </c>
       <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>10500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,474 +656,486 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44751</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44555</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44387</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44275</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44191</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44107</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44023</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43911</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43743</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43659</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43547</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43379</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43295</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43183</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43015</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42931</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42819</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E8" s="3">
         <v>67700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>57300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>65500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>73400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>56900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>72100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>74900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>94300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>72400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>73400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>81300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>99700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>59200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>74800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>78100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>83500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>47000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>45800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>55600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>32100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>51000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>44000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>48700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>32100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>52200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>41900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>53900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>31900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>49800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E9" s="3">
         <v>50900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>47400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>43000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>49600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>55200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>51100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>56000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>61300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>70600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>52300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>57100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>63000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>74600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>41800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>56900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>54500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>60300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>36200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>35700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>42700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>23600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>38800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>31600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>37200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>40200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>30500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>40800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>39600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E10" s="3">
         <v>16800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>20100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>25100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>10200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>12400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>11500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>12000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>11400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>13100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1160,13 +1172,14 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>3200</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1174,11 +1187,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>3100</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1264,8 +1277,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1368,16 +1384,19 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3900</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1394,8 +1413,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1464,24 +1483,27 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>-300</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>600</v>
+      </c>
+      <c r="E15" s="3">
         <v>1000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>600</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
@@ -1499,40 +1521,40 @@
         <v>600</v>
       </c>
       <c r="K15" s="3">
+        <v>600</v>
+      </c>
+      <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
-      </c>
-      <c r="O15" s="3">
-        <v>400</v>
       </c>
       <c r="P15" s="3">
         <v>400</v>
       </c>
       <c r="Q15" s="3">
+        <v>400</v>
+      </c>
+      <c r="R15" s="3">
         <v>600</v>
-      </c>
-      <c r="R15" s="3">
-        <v>400</v>
       </c>
       <c r="S15" s="3">
         <v>400</v>
       </c>
       <c r="T15" s="3">
+        <v>400</v>
+      </c>
+      <c r="U15" s="3">
         <v>300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>400</v>
-      </c>
-      <c r="V15" s="3">
-        <v>300</v>
       </c>
       <c r="W15" s="3">
         <v>300</v>
@@ -1541,10 +1563,10 @@
         <v>300</v>
       </c>
       <c r="Y15" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z15" s="3">
         <v>500</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>300</v>
       </c>
       <c r="AA15" s="3">
         <v>300</v>
@@ -1553,22 +1575,22 @@
         <v>300</v>
       </c>
       <c r="AC15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD15" s="3">
         <v>400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>300</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>400</v>
       </c>
       <c r="AF15" s="3">
         <v>400</v>
       </c>
       <c r="AG15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH15" s="3">
         <v>500</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>400</v>
       </c>
       <c r="AI15" s="3">
         <v>400</v>
@@ -1576,8 +1598,11 @@
       <c r="AJ15" s="3">
         <v>400</v>
       </c>
+      <c r="AK15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1611,216 +1636,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E17" s="3">
         <v>63700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>54200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>60500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>66900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>61500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>56800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>67300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>70700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>86100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>63400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>67000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>73600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>89000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>52100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>67800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>65300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>72700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>34900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>43500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>42900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>53200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>31700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>46000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>38800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>46700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>30400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>47100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>37800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>50600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>29600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>46100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E18" s="3">
         <v>4100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>9000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>3300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1857,13 +1889,14 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1884,25 +1917,25 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -1938,31 +1971,34 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>13100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1973,162 +2009,165 @@
         <v>5100</v>
       </c>
       <c r="F21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G21" s="3">
         <v>3700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>5800</v>
       </c>
       <c r="L21" s="3">
         <v>5800</v>
       </c>
       <c r="M21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="N21" s="3">
         <v>10300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>12300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>8300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>13900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>16200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>2600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>6800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>4700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
         <v>500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>700</v>
       </c>
       <c r="F22" s="3">
         <v>700</v>
       </c>
       <c r="G22" s="3">
+        <v>700</v>
+      </c>
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
-      </c>
-      <c r="P22" s="3">
-        <v>400</v>
       </c>
       <c r="Q22" s="3">
         <v>400</v>
       </c>
       <c r="R22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X22" s="3">
         <v>100</v>
@@ -2140,13 +2179,13 @@
         <v>100</v>
       </c>
       <c r="AA22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
       <c r="AC22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="3">
         <v>200</v>
@@ -2169,216 +2208,225 @@
       <c r="AJ22" s="3">
         <v>200</v>
       </c>
+      <c r="AK22" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E23" s="3">
         <v>7500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>6900</v>
       </c>
       <c r="S23" s="3">
         <v>6900</v>
       </c>
       <c r="T23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="U23" s="3">
         <v>12800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>14900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2481,216 +2529,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>5700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E27" s="3">
         <v>5700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2793,8 +2850,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2849,17 +2909,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2867,23 +2927,23 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>3000</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2891,14 +2951,17 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3001,8 +3064,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3105,13 +3171,16 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -3132,25 +3201,25 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3186,135 +3255,141 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>5700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>300</v>
-      </c>
-      <c r="AA33" s="3">
-        <v>3600</v>
       </c>
       <c r="AB33" s="3">
         <v>3600</v>
       </c>
       <c r="AC33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AD33" s="3">
         <v>12100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3417,221 +3492,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>5700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>300</v>
-      </c>
-      <c r="AA35" s="3">
-        <v>3600</v>
       </c>
       <c r="AB35" s="3">
         <v>3600</v>
       </c>
       <c r="AC35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AD35" s="3">
         <v>12100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44751</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44555</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44387</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44275</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44191</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44107</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44023</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43911</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43743</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43659</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43547</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43379</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43295</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43183</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43015</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42931</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42819</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3668,8 +3752,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3706,112 +3791,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>400</v>
+        <v>4200</v>
       </c>
       <c r="E41" s="3">
         <v>400</v>
       </c>
       <c r="F41" s="3">
+        <v>400</v>
+      </c>
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
       <c r="H41" s="3">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3">
         <v>900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6100</v>
-      </c>
-      <c r="K41" s="3">
-        <v>4000</v>
       </c>
       <c r="L41" s="3">
         <v>4000</v>
       </c>
       <c r="M41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N41" s="3">
         <v>6200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2900</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>1600</v>
       </c>
       <c r="AF41" s="3">
         <v>1600</v>
       </c>
       <c r="AG41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AH41" s="3">
         <v>2300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3914,424 +4003,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E43" s="3">
         <v>53500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>47800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>52300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>63400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>55000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>50500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>57400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>66300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>60600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>67300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>66700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>68800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>52200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>54500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>65300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>63800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>49500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>32600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>35600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>37200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>36900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>33000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>41800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>36500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>30800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>29400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>40100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>35300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>33000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>29300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>36700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E44" s="3">
         <v>85500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>86600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>96000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>92500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>105300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>111700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>122500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>121900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>135000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>130200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>114600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>92400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>91800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>86600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>91400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>72500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>63700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>41700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>42200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>42300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>48400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>48000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>47700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>39100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>45700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>41500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>40100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>35200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>42400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>37500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>37200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>500</v>
+      </c>
+      <c r="E45" s="3">
         <v>200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2700</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>3000</v>
       </c>
       <c r="Z45" s="3">
         <v>3000</v>
       </c>
       <c r="AA45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AB45" s="3">
         <v>4200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3000</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>2900</v>
       </c>
       <c r="AD45" s="3">
         <v>2900</v>
       </c>
       <c r="AE45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AF45" s="3">
         <v>3400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>133800</v>
+      </c>
+      <c r="E46" s="3">
         <v>144700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>139100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>151500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>146800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>175900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>172700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>184000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>188200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>209400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>204300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>201000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>171100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>173600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>154300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>155800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>145400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>136900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>109900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>83600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>86900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>93600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>92500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>88000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>87900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>96300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>90600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>75200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>80300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>82800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>75800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>71900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>75600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4356,8 +4460,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4414,236 +4518,245 @@
         <v>0</v>
       </c>
       <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
         <v>20200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>20300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>19600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>18500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>17400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E48" s="3">
         <v>30500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>21100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>17300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>16100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>15500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>14300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13500</v>
-      </c>
-      <c r="AI48" s="3">
-        <v>13700</v>
       </c>
       <c r="AJ48" s="3">
         <v>13700</v>
       </c>
+      <c r="AK48" s="3">
+        <v>13700</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68200</v>
+      </c>
+      <c r="E49" s="3">
         <v>68700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>69800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>70400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>71000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>72200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>73400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>73900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>74600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>75000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>53500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>53900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>54300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>54900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>55300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>44500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>44800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>45300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>45600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>45900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>46300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>45800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>46200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>40200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>40500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>40900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>41200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>41600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>42000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>42500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>42300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4746,8 +4859,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4850,37 +4966,40 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>2900</v>
       </c>
       <c r="F52" s="3">
         <v>2900</v>
       </c>
       <c r="G52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H52" s="3">
         <v>3000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>3200</v>
       </c>
       <c r="K52" s="3">
         <v>3200</v>
       </c>
       <c r="L52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="M52" s="3">
         <v>300</v>
@@ -4889,7 +5008,7 @@
         <v>300</v>
       </c>
       <c r="O52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
@@ -4904,10 +5023,10 @@
         <v>100</v>
       </c>
       <c r="T52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V52" s="3">
         <v>100</v>
@@ -4925,7 +5044,7 @@
         <v>100</v>
       </c>
       <c r="AA52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
@@ -4940,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="AF52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG52" s="3">
         <v>100</v>
@@ -4952,10 +5071,13 @@
         <v>100</v>
       </c>
       <c r="AJ52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5058,112 +5180,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>226300</v>
+      </c>
+      <c r="E54" s="3">
         <v>244900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>243100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>256300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>253000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>283400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>281100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>293600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>298700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>320300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>316900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>307100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>251800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>254200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>231600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>232000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>220700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>198700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>170900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>145400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>148800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>156000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>155500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>150300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>149500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>149800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>144100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>150200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>156100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>158200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>150200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>145300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>150800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5200,8 +5328,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5238,117 +5367,121 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E57" s="3">
         <v>20000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>22700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>32100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>6900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>5200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>4300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8200</v>
+        <v>7600</v>
       </c>
       <c r="E58" s="3">
         <v>8200</v>
@@ -5363,13 +5496,13 @@
         <v>8200</v>
       </c>
       <c r="I58" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="J58" s="3">
         <v>8100</v>
       </c>
       <c r="K58" s="3">
-        <v>7100</v>
+        <v>8100</v>
       </c>
       <c r="L58" s="3">
         <v>7100</v>
@@ -5389,12 +5522,12 @@
       <c r="Q58" s="3">
         <v>7100</v>
       </c>
-      <c r="R58" s="3" t="s">
+      <c r="R58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
@@ -5405,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X58" s="3">
         <v>100</v>
@@ -5414,7 +5547,7 @@
         <v>100</v>
       </c>
       <c r="Z58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -5426,10 +5559,10 @@
         <v>0</v>
       </c>
       <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>1300</v>
       </c>
       <c r="AF58" s="3">
         <v>1300</v>
@@ -5444,10 +5577,13 @@
         <v>1300</v>
       </c>
       <c r="AJ58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AK58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5457,11 +5593,11 @@
       <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>400</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
@@ -5472,244 +5608,250 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>22400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>10300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>8400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>7100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>11100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>14000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E60" s="3">
         <v>42000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>34100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>32700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>35900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>38900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>49700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>53000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>56100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>48200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>51400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>38400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>37700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>46100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>53200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>33700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>18200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>15700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>16700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>20400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>32300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>19500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>22000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>15100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E61" s="3">
         <v>29500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>43400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>54000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>73100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>85000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>96500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>87700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>99600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>94000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>92900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>51900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>42900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>46900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>30100</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -5720,17 +5862,17 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>5200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3700</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
       <c r="AB61" s="3">
         <v>0</v>
       </c>
@@ -5738,28 +5880,31 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>3800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>21900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>24700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>22400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>23000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5770,7 +5915,7 @@
         <v>300</v>
       </c>
       <c r="F62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G62" s="3">
         <v>400</v>
@@ -5785,58 +5930,58 @@
         <v>400</v>
       </c>
       <c r="K62" s="3">
+        <v>400</v>
+      </c>
+      <c r="L62" s="3">
         <v>13600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4400</v>
-      </c>
-      <c r="X62" s="3">
-        <v>5100</v>
       </c>
       <c r="Y62" s="3">
         <v>5100</v>
       </c>
       <c r="Z62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AA62" s="3">
         <v>4800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4500</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>3000</v>
       </c>
       <c r="AC62" s="3">
         <v>3000</v>
@@ -5848,22 +5993,25 @@
         <v>3000</v>
       </c>
       <c r="AF62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG62" s="3">
         <v>5400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>6400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5966,8 +6114,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6070,8 +6221,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6174,112 +6328,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E66" s="3">
         <v>74900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>77100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>91600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>88400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>122200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>122700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>137300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>140200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>163000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>160900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>155400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>105200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>109400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>86500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>90100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>81500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>57700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>38300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>20300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>22600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>28300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>23300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>19600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>39000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>44400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>52100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>46200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>43100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>49000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6316,8 +6476,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6420,8 +6581,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6524,8 +6688,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6628,8 +6795,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6732,112 +6902,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E72" s="3">
         <v>164200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>160600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>159800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>160100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>147400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>144700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>142600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>144900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>143700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>142400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>138000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>133100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>131200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>131400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>128000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>125200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>126900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>118400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>111100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>112000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>111800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>112800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>112500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>113900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>112000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>110100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>99500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>99900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>94000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>92400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>91600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>91700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6940,8 +7116,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7044,8 +7223,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7148,112 +7330,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>169000</v>
+      </c>
+      <c r="E76" s="3">
         <v>170100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>166000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>164700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>164600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>161200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>158400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>156300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>158500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>157300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>156000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>151600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>146600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>144700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>145100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>141900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>139200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>141000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>132600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>125200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>126200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>126100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>127200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>127000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>128300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>126400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>124600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>111200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>111700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>106100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>104100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>102200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>101700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7356,221 +7544,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44751</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44555</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44387</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44275</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44191</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44107</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44023</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43911</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43743</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43659</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43547</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43379</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43295</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43183</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43015</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42931</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42819</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>5700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>300</v>
-      </c>
-      <c r="AA81" s="3">
-        <v>3600</v>
       </c>
       <c r="AB81" s="3">
         <v>3600</v>
       </c>
       <c r="AC81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AD81" s="3">
         <v>12100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7607,8 +7804,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7622,97 +7820,100 @@
         <v>800</v>
       </c>
       <c r="G83" s="3">
+        <v>800</v>
+      </c>
+      <c r="H83" s="3">
         <v>400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
-      </c>
-      <c r="J83" s="3">
-        <v>900</v>
       </c>
       <c r="K83" s="3">
         <v>900</v>
       </c>
       <c r="L83" s="3">
+        <v>900</v>
+      </c>
+      <c r="M83" s="3">
         <v>1600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7815,8 +8016,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7919,8 +8123,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8023,8 +8230,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8127,8 +8337,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8231,112 +8444,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E89" s="3">
         <v>10500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13300</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>20600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>14800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-5900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>8900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>7000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8373,112 +8592,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-500</v>
       </c>
       <c r="H91" s="3">
         <v>-500</v>
       </c>
       <c r="I91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB91" s="3">
         <v>-1000</v>
       </c>
       <c r="AC91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-400</v>
       </c>
       <c r="AJ91" s="3">
         <v>-400</v>
       </c>
+      <c r="AK91" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8581,8 +8804,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8685,112 +8911,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>5400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>34100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8827,8 +9059,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8842,10 +9075,10 @@
         <v>2100</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H96" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>2100</v>
@@ -8854,7 +9087,7 @@
         <v>2100</v>
       </c>
       <c r="K96" s="3">
-        <v>-2000</v>
+        <v>2100</v>
       </c>
       <c r="L96" s="3">
         <v>-2000</v>
@@ -8866,7 +9099,7 @@
         <v>-2000</v>
       </c>
       <c r="O96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="P96" s="3">
         <v>-1900</v>
@@ -8875,7 +9108,7 @@
         <v>-1900</v>
       </c>
       <c r="R96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="S96" s="3">
         <v>-2000</v>
@@ -8884,7 +9117,7 @@
         <v>-2000</v>
       </c>
       <c r="U96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="V96" s="3">
         <v>-1800</v>
@@ -8914,7 +9147,7 @@
         <v>-1800</v>
       </c>
       <c r="AE96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AF96" s="3">
         <v>-1700</v>
@@ -8926,13 +9159,16 @@
         <v>-1700</v>
       </c>
       <c r="AI96" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AJ96" s="3">
         <v>-1600</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-1600</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9035,8 +9271,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9139,8 +9378,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9243,112 +9485,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-14000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>40200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>14000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>22800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-3100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-7900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-5900</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>1900</v>
       </c>
       <c r="Z100" s="3">
         <v>1900</v>
       </c>
       <c r="AA100" s="3">
-        <v>-1800</v>
+        <v>1900</v>
       </c>
       <c r="AB100" s="3">
         <v>-1800</v>
       </c>
       <c r="AC100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-24300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9373,8 +9621,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9451,108 +9699,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>3800</v>
       </c>
       <c r="E102" s="3">
         <v>100</v>
       </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>10500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>12700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,486 +656,499 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44751</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44387</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44275</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44191</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44107</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44023</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43911</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43743</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43659</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43547</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43379</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43295</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43183</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43015</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42931</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42819</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E8" s="3">
         <v>63900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>62500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>57300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>65500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>73400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>67800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>56900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>72100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>74900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>94300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>72400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>73400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>81300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>99700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>59200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>74800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>78100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>83500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>37300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>47000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>45800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>55600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>32100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>51000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>44000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>48700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>32100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>52200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>41900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>53900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>31900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>49800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E9" s="3">
         <v>48000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>50900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>47400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>49600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>55200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>51100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>45900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>56000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>61300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>70600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>52300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>57100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>63000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>74600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>41800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>56900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>54500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>60300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>36200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>35700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>42700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>23600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>38800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>31600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>37200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>40200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>30500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>40800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>39600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E10" s="3">
         <v>15900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>16100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>23700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>20100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>25100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>17900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>23600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>10200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>12900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>12200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>11500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>12000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>13100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>10200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1173,16 +1186,17 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>3200</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1190,11 +1204,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>3100</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1280,8 +1294,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1387,19 +1404,22 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-3900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1416,8 +1436,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1486,16 +1506,19 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>-300</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1503,10 +1526,10 @@
         <v>600</v>
       </c>
       <c r="E15" s="3">
+        <v>600</v>
+      </c>
+      <c r="F15" s="3">
         <v>1000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>600</v>
       </c>
       <c r="G15" s="3">
         <v>600</v>
@@ -1524,40 +1547,40 @@
         <v>600</v>
       </c>
       <c r="L15" s="3">
+        <v>600</v>
+      </c>
+      <c r="M15" s="3">
         <v>500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>600</v>
-      </c>
-      <c r="P15" s="3">
-        <v>400</v>
       </c>
       <c r="Q15" s="3">
         <v>400</v>
       </c>
       <c r="R15" s="3">
+        <v>400</v>
+      </c>
+      <c r="S15" s="3">
         <v>600</v>
-      </c>
-      <c r="S15" s="3">
-        <v>400</v>
       </c>
       <c r="T15" s="3">
         <v>400</v>
       </c>
       <c r="U15" s="3">
+        <v>400</v>
+      </c>
+      <c r="V15" s="3">
         <v>300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>400</v>
-      </c>
-      <c r="W15" s="3">
-        <v>300</v>
       </c>
       <c r="X15" s="3">
         <v>300</v>
@@ -1566,10 +1589,10 @@
         <v>300</v>
       </c>
       <c r="Z15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA15" s="3">
         <v>500</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>300</v>
       </c>
       <c r="AB15" s="3">
         <v>300</v>
@@ -1578,22 +1601,22 @@
         <v>300</v>
       </c>
       <c r="AD15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE15" s="3">
         <v>400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>300</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>400</v>
       </c>
       <c r="AG15" s="3">
         <v>400</v>
       </c>
       <c r="AH15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI15" s="3">
         <v>500</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>400</v>
       </c>
       <c r="AJ15" s="3">
         <v>400</v>
@@ -1601,8 +1624,11 @@
       <c r="AK15" s="3">
         <v>400</v>
       </c>
+      <c r="AL15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1637,222 +1663,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51800</v>
+      </c>
+      <c r="E17" s="3">
         <v>59400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>63700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>58100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>54200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>60500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>66900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>61500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>56800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>67300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>70700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>86100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>67000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>73600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>89000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>52100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>67800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>65300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>72700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>34900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>43500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>42900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>53200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>46000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>38800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>46700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>30400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>47100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>37800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>50600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>29600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>46100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>4500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>9000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>3300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1890,17 +1923,18 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1920,25 +1954,25 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1974,36 +2008,39 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>13100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5100</v>
+        <v>4300</v>
       </c>
       <c r="E21" s="3">
         <v>5100</v>
@@ -2012,165 +2049,168 @@
         <v>5100</v>
       </c>
       <c r="G21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H21" s="3">
         <v>3700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>5800</v>
       </c>
       <c r="M21" s="3">
         <v>5800</v>
       </c>
       <c r="N21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="O21" s="3">
         <v>10300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>8300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>13900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>6100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>16200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>2600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>4700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>700</v>
       </c>
       <c r="G22" s="3">
         <v>700</v>
       </c>
       <c r="H22" s="3">
+        <v>700</v>
+      </c>
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>400</v>
       </c>
       <c r="R22" s="3">
         <v>400</v>
       </c>
       <c r="S22" s="3">
+        <v>400</v>
+      </c>
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
@@ -2182,13 +2222,13 @@
         <v>100</v>
       </c>
       <c r="AB22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
       <c r="AD22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="3">
         <v>200</v>
@@ -2211,222 +2251,231 @@
       <c r="AK22" s="3">
         <v>200</v>
       </c>
+      <c r="AL22" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>4300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>6900</v>
       </c>
       <c r="T23" s="3">
         <v>6900</v>
       </c>
       <c r="U23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V23" s="3">
         <v>12800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>14900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>3100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2532,222 +2581,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E26" s="3">
         <v>2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>8100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>12100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E27" s="3">
         <v>2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2853,8 +2911,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2912,17 +2973,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2930,23 +2991,23 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-600</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>3000</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2954,14 +3015,17 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3067,8 +3131,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3174,17 +3241,20 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -3204,25 +3274,25 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -3258,138 +3328,144 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E33" s="3">
         <v>2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>300</v>
-      </c>
-      <c r="AB33" s="3">
-        <v>3600</v>
       </c>
       <c r="AC33" s="3">
         <v>3600</v>
       </c>
       <c r="AD33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AE33" s="3">
         <v>12100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3495,227 +3571,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E35" s="3">
         <v>2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>300</v>
-      </c>
-      <c r="AB35" s="3">
-        <v>3600</v>
       </c>
       <c r="AC35" s="3">
         <v>3600</v>
       </c>
       <c r="AD35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AE35" s="3">
         <v>12100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44751</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44387</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44275</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44191</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44107</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44023</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43911</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43743</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43659</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43547</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43379</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43295</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43183</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43015</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42931</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42819</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3753,8 +3838,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3792,115 +3878,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E41" s="3">
         <v>4200</v>
-      </c>
-      <c r="E41" s="3">
-        <v>400</v>
       </c>
       <c r="F41" s="3">
         <v>400</v>
       </c>
       <c r="G41" s="3">
+        <v>400</v>
+      </c>
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
         <v>900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6100</v>
-      </c>
-      <c r="L41" s="3">
-        <v>4000</v>
       </c>
       <c r="M41" s="3">
         <v>4000</v>
       </c>
       <c r="N41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O41" s="3">
         <v>6200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>16700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2900</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>1600</v>
       </c>
       <c r="AG41" s="3">
         <v>1600</v>
       </c>
       <c r="AH41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AI41" s="3">
         <v>2300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4006,436 +4096,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E43" s="3">
         <v>48800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>53500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>47800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>52300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>50000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>63400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>55000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>50500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>57400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>66300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>60600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>67300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>68800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>52200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>54500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>65300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>63800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>49500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>35600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>37200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>36900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>33000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>41800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>36500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>30800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>29400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>40100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>35300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>33000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>29300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>36700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E44" s="3">
         <v>76000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>85500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>86600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>96000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>92500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>105300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>111700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>122500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>121900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>135000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>130200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>114600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>92400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>91800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>86600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>91400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>72500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>63700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>41700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>42200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>42300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>48400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>48000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>47700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>39100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>45700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>41500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>40100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>35200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>42400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>37500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>37200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>33800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2700</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>3000</v>
       </c>
       <c r="AA45" s="3">
         <v>3000</v>
       </c>
       <c r="AB45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AC45" s="3">
         <v>4200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3000</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>2900</v>
       </c>
       <c r="AE45" s="3">
         <v>2900</v>
       </c>
       <c r="AF45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AG45" s="3">
         <v>3400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>131100</v>
+      </c>
+      <c r="E46" s="3">
         <v>133800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>144700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>139100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>151500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>146800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>175900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>172700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>184000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>188200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>209400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>204300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>201000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>171100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>173600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>154300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>155800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>145400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>136900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>109900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>83600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>86900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>93600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>92500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>88000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>87900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>96300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>90600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>75200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>80300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>82800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>75800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>71900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>75600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4463,8 +4568,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4521,242 +4626,251 @@
         <v>0</v>
       </c>
       <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
         <v>20200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>20300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>19600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>18500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>17400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>19000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23200</v>
+      </c>
+      <c r="E48" s="3">
         <v>23400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>21100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>17300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>16100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>14300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13500</v>
-      </c>
-      <c r="AJ48" s="3">
-        <v>13700</v>
       </c>
       <c r="AK48" s="3">
         <v>13700</v>
       </c>
+      <c r="AL48" s="3">
+        <v>13700</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E49" s="3">
         <v>68200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>68700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>69800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>70400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>71000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>73400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>73900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>75000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>53500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>53900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>54300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>54900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>55300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>44500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>44800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>45300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>45600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>45900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>46300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>45800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>46200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>40200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>40500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>40900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>41200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>41600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>42000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>42500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>42300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4862,8 +4976,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4969,40 +5086,43 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>200</v>
+      </c>
+      <c r="E52" s="3">
         <v>900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2900</v>
       </c>
       <c r="G52" s="3">
         <v>2900</v>
       </c>
       <c r="H52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I52" s="3">
         <v>3000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>3200</v>
       </c>
       <c r="L52" s="3">
         <v>3200</v>
       </c>
       <c r="M52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="N52" s="3">
         <v>300</v>
@@ -5011,7 +5131,7 @@
         <v>300</v>
       </c>
       <c r="P52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
@@ -5026,10 +5146,10 @@
         <v>100</v>
       </c>
       <c r="U52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W52" s="3">
         <v>100</v>
@@ -5047,7 +5167,7 @@
         <v>100</v>
       </c>
       <c r="AB52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -5062,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="AG52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH52" s="3">
         <v>100</v>
@@ -5074,10 +5194,13 @@
         <v>100</v>
       </c>
       <c r="AK52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5183,115 +5306,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>222100</v>
+      </c>
+      <c r="E54" s="3">
         <v>226300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>244900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>243100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>256300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>253000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>283400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>281100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>293600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>298700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>320300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>316900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>307100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>251800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>254200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>231600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>232000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>220700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>198700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>170900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>145400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>148800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>156000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>155500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>150300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>149500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>149800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>144100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>150200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>156100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>158200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>150200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>145300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>150800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5329,8 +5458,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5368,115 +5498,119 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E57" s="3">
         <v>11900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>14700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>20900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>32100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>6400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>7200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>5600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>6600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5484,7 +5618,7 @@
         <v>7600</v>
       </c>
       <c r="E58" s="3">
-        <v>8200</v>
+        <v>7600</v>
       </c>
       <c r="F58" s="3">
         <v>8200</v>
@@ -5499,13 +5633,13 @@
         <v>8200</v>
       </c>
       <c r="J58" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="K58" s="3">
         <v>8100</v>
       </c>
       <c r="L58" s="3">
-        <v>7100</v>
+        <v>8100</v>
       </c>
       <c r="M58" s="3">
         <v>7100</v>
@@ -5525,12 +5659,12 @@
       <c r="R58" s="3">
         <v>7100</v>
       </c>
-      <c r="S58" s="3" t="s">
+      <c r="S58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
@@ -5541,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="3">
         <v>100</v>
@@ -5550,7 +5684,7 @@
         <v>100</v>
       </c>
       <c r="AA58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5562,10 +5696,10 @@
         <v>0</v>
       </c>
       <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>1300</v>
       </c>
       <c r="AG58" s="3">
         <v>1300</v>
@@ -5580,15 +5714,18 @@
         <v>1300</v>
       </c>
       <c r="AK58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AL58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>300</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>8</v>
@@ -5596,11 +5733,11 @@
       <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
         <v>400</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
@@ -5611,250 +5748,256 @@
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>22400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>25100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>21100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>8400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>7100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>9700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>14000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>12800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E60" s="3">
         <v>34500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>42000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>44200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>38900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>49700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>53000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>56100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>48200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>51400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>38400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>37700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>46100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>53200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>33700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>15500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>18200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>19600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>15700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>16700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>20400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>16600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>32300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>19500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>22000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>15100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>18400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E61" s="3">
         <v>19200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>29500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>43400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>73100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>85000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>96500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>87700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>99600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>94000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>92900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>50400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>51900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>42900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>46900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>30100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -5865,17 +6008,17 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>5200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3700</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5883,28 +6026,31 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>3800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>21900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>24700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>22400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>23000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>24200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5918,7 +6064,7 @@
         <v>300</v>
       </c>
       <c r="G62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H62" s="3">
         <v>400</v>
@@ -5933,58 +6079,58 @@
         <v>400</v>
       </c>
       <c r="L62" s="3">
+        <v>400</v>
+      </c>
+      <c r="M62" s="3">
         <v>13600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>4500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4400</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>5100</v>
       </c>
       <c r="Z62" s="3">
         <v>5100</v>
       </c>
       <c r="AA62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AB62" s="3">
         <v>4800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4500</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>3000</v>
       </c>
       <c r="AD62" s="3">
         <v>3000</v>
@@ -5996,22 +6142,25 @@
         <v>3000</v>
       </c>
       <c r="AG62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AH62" s="3">
         <v>5400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>6400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6117,8 +6266,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6224,8 +6376,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6331,115 +6486,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E66" s="3">
         <v>57300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>74900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>77100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>91600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>88400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>122200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>122700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>137300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>140200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>163000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>160900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>155400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>105200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>109400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>86500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>90100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>81500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>57700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>20300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>22600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>29900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>28300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>23300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>21200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>23400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>19600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>39000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>44400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>52100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>46200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>43100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>49000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6477,8 +6638,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6584,8 +6746,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6691,8 +6856,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6798,8 +6966,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6905,115 +7076,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>165300</v>
+      </c>
+      <c r="E72" s="3">
         <v>164800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>164200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>160600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>159800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>160100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>147400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>144700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>142600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>144900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>143700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>142400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>138000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>133100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>131200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>131400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>128000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>125200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>126900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>118400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>111100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>112000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>111800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>112800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>112500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>113900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>112000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>110100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>99500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>99900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>94000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>92400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>91600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>91700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7119,8 +7296,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7226,8 +7406,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7333,115 +7516,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>168800</v>
+      </c>
+      <c r="E76" s="3">
         <v>169000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>170100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>166000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>164700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>164600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>161200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>158400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>156300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>158500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>157300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>156000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>151600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>146600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>144700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>145100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>141900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>139200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>141000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>132600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>125200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>126200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>126100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>127200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>127000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>128300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>126400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>124600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>111200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>111700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>106100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>104100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>102200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>101700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7547,227 +7736,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44751</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44387</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44275</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44191</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44107</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44023</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43911</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43743</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43659</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43547</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43379</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43295</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43183</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43015</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42931</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42819</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E81" s="3">
         <v>2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>300</v>
-      </c>
-      <c r="AB81" s="3">
-        <v>3600</v>
       </c>
       <c r="AC81" s="3">
         <v>3600</v>
       </c>
       <c r="AD81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AE81" s="3">
         <v>12100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7805,8 +8003,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7823,97 +8022,100 @@
         <v>800</v>
       </c>
       <c r="H83" s="3">
+        <v>800</v>
+      </c>
+      <c r="I83" s="3">
         <v>400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>900</v>
       </c>
       <c r="L83" s="3">
         <v>900</v>
       </c>
       <c r="M83" s="3">
+        <v>900</v>
+      </c>
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8019,8 +8221,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8126,8 +8331,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8233,8 +8441,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8340,8 +8551,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8447,115 +8661,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>12300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13300</v>
       </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>20600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-5900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>12900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>10300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8593,115 +8813,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-500</v>
       </c>
       <c r="I91" s="3">
         <v>-500</v>
       </c>
       <c r="J91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-1000</v>
       </c>
       <c r="AC91" s="3">
         <v>-1000</v>
       </c>
       <c r="AD91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-400</v>
       </c>
       <c r="AK91" s="3">
         <v>-400</v>
       </c>
+      <c r="AL91" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8807,8 +9031,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8914,115 +9141,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>5400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-17800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>34100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9060,8 +9293,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9078,10 +9312,10 @@
         <v>2100</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="I96" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
         <v>2100</v>
@@ -9090,7 +9324,7 @@
         <v>2100</v>
       </c>
       <c r="L96" s="3">
-        <v>-2000</v>
+        <v>2100</v>
       </c>
       <c r="M96" s="3">
         <v>-2000</v>
@@ -9102,7 +9336,7 @@
         <v>-2000</v>
       </c>
       <c r="P96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="Q96" s="3">
         <v>-1900</v>
@@ -9111,7 +9345,7 @@
         <v>-1900</v>
       </c>
       <c r="S96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="T96" s="3">
         <v>-2000</v>
@@ -9120,7 +9354,7 @@
         <v>-2000</v>
       </c>
       <c r="V96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="W96" s="3">
         <v>-1800</v>
@@ -9150,7 +9384,7 @@
         <v>-1800</v>
       </c>
       <c r="AF96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AG96" s="3">
         <v>-1700</v>
@@ -9162,13 +9396,16 @@
         <v>-1700</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AK96" s="3">
         <v>-1600</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-1600</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9274,8 +9511,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9381,8 +9621,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9488,115 +9731,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>40200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>14000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>22800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5900</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>1900</v>
       </c>
       <c r="AA100" s="3">
         <v>1900</v>
       </c>
       <c r="AB100" s="3">
-        <v>-1800</v>
+        <v>1900</v>
       </c>
       <c r="AC100" s="3">
         <v>-1800</v>
       </c>
       <c r="AD100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-24300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9624,8 +9873,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9702,111 +9951,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>3800</v>
-      </c>
-      <c r="E102" s="3">
-        <v>100</v>
       </c>
       <c r="F102" s="3">
         <v>100</v>
       </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2100</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>10500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,499 +656,512 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44751</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44639</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44387</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44275</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44191</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44107</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44023</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43911</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43743</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43659</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43547</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43379</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43295</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43183</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43015</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42931</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42819</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E8" s="3">
         <v>55500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>63900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>67700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>62500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>57300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>65500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>73400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>67800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>56900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>72100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>74900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>94300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>72400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>73400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>99700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>59200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>74800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>78100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>83500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>47000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>45800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>55600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>32100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>51000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>44000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>48700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>32100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>52200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>41900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>53900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>31900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>49800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E9" s="3">
         <v>40700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>48000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>50900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>47400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>43000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>49600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>55200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>51100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>45900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>56000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>61300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>70600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>52300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>57100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>63000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>74600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>41800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>56900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>54500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>60300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>36200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>35700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>42700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>23600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>38800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>31600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>37200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>23200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>40200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>30500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>40800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>23600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>39600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E10" s="3">
         <v>14800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>16800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>14400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>18100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>16100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>18300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>25100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>17400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>17900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>23600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>23200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>10200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>10800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>12400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>11500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>12000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>11400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>13100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>8300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>10200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1187,19 +1200,20 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>3200</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1207,11 +1221,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>3100</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1297,8 +1311,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1407,22 +1424,25 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-3900</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1439,8 +1459,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1509,16 +1529,19 @@
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-300</v>
-      </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1529,10 +1552,10 @@
         <v>600</v>
       </c>
       <c r="F15" s="3">
+        <v>600</v>
+      </c>
+      <c r="G15" s="3">
         <v>1000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>600</v>
       </c>
       <c r="H15" s="3">
         <v>600</v>
@@ -1550,40 +1573,40 @@
         <v>600</v>
       </c>
       <c r="M15" s="3">
+        <v>600</v>
+      </c>
+      <c r="N15" s="3">
         <v>500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>600</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>400</v>
       </c>
       <c r="R15" s="3">
         <v>400</v>
       </c>
       <c r="S15" s="3">
+        <v>400</v>
+      </c>
+      <c r="T15" s="3">
         <v>600</v>
-      </c>
-      <c r="T15" s="3">
-        <v>400</v>
       </c>
       <c r="U15" s="3">
         <v>400</v>
       </c>
       <c r="V15" s="3">
+        <v>400</v>
+      </c>
+      <c r="W15" s="3">
         <v>300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>400</v>
-      </c>
-      <c r="X15" s="3">
-        <v>300</v>
       </c>
       <c r="Y15" s="3">
         <v>300</v>
@@ -1592,10 +1615,10 @@
         <v>300</v>
       </c>
       <c r="AA15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB15" s="3">
         <v>500</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>300</v>
       </c>
       <c r="AC15" s="3">
         <v>300</v>
@@ -1604,22 +1627,22 @@
         <v>300</v>
       </c>
       <c r="AE15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF15" s="3">
         <v>400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>300</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>400</v>
       </c>
       <c r="AH15" s="3">
         <v>400</v>
       </c>
       <c r="AI15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>500</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>400</v>
       </c>
       <c r="AK15" s="3">
         <v>400</v>
@@ -1627,8 +1650,11 @@
       <c r="AL15" s="3">
         <v>400</v>
       </c>
+      <c r="AM15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1664,228 +1690,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E17" s="3">
         <v>51800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>59400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>63700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>58100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>54200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>60500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>66900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>61500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>56800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>67300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>70700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>86100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>63400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>67000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>73600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>89000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>52100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>67800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>65300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>72700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>34900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>43500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>42900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>53200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>31700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>46000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>38800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>46700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>30400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>47100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>37800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>50600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>29600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>46100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E18" s="3">
         <v>3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>8200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>9000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1924,20 +1957,21 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1957,25 +1991,25 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -2011,39 +2045,42 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>13100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>4300</v>
-      </c>
-      <c r="E21" s="3">
-        <v>5100</v>
       </c>
       <c r="F21" s="3">
         <v>5100</v>
@@ -2052,100 +2089,103 @@
         <v>5100</v>
       </c>
       <c r="H21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="I21" s="3">
         <v>3700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>800</v>
-      </c>
-      <c r="M21" s="3">
-        <v>5800</v>
       </c>
       <c r="N21" s="3">
         <v>5800</v>
       </c>
       <c r="O21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P21" s="3">
         <v>10300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>10500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>8300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>13900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>6100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>16200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>2600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>5400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2153,67 +2193,67 @@
         <v>200</v>
       </c>
       <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>700</v>
       </c>
       <c r="H22" s="3">
         <v>700</v>
       </c>
       <c r="I22" s="3">
+        <v>700</v>
+      </c>
+      <c r="J22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>500</v>
-      </c>
-      <c r="R22" s="3">
-        <v>400</v>
       </c>
       <c r="S22" s="3">
         <v>400</v>
       </c>
       <c r="T22" s="3">
+        <v>400</v>
+      </c>
+      <c r="U22" s="3">
         <v>200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="3">
         <v>100</v>
@@ -2225,13 +2265,13 @@
         <v>100</v>
       </c>
       <c r="AC22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
       <c r="AE22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="3">
         <v>200</v>
@@ -2254,228 +2294,237 @@
       <c r="AL22" s="3">
         <v>200</v>
       </c>
+      <c r="AM22" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10300</v>
-      </c>
-      <c r="T23" s="3">
-        <v>6900</v>
       </c>
       <c r="U23" s="3">
         <v>6900</v>
       </c>
       <c r="V23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="W23" s="3">
         <v>12800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>14900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2584,228 +2633,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>2600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>8700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>12100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="3">
         <v>2600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>10200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2914,8 +2972,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2976,17 +3037,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2994,23 +3055,23 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-600</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>3000</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3018,14 +3079,17 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL29" s="3" t="s">
+      <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3134,8 +3198,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3244,20 +3311,23 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -3277,25 +3347,25 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -3331,141 +3401,147 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E33" s="3">
         <v>2600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>10200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>300</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>3600</v>
       </c>
       <c r="AD33" s="3">
         <v>3600</v>
       </c>
       <c r="AE33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AF33" s="3">
         <v>12100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3574,233 +3650,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E35" s="3">
         <v>2600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>10200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>300</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>3600</v>
       </c>
       <c r="AD35" s="3">
         <v>3600</v>
       </c>
       <c r="AE35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AF35" s="3">
         <v>12100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44751</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44639</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44387</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44275</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44191</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44107</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44023</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43911</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43743</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43659</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43547</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43379</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43295</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43183</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43015</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42931</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42819</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3839,8 +3924,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3879,118 +3965,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>400</v>
       </c>
       <c r="G41" s="3">
         <v>400</v>
       </c>
       <c r="H41" s="3">
+        <v>400</v>
+      </c>
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
       <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6100</v>
-      </c>
-      <c r="M41" s="3">
-        <v>4000</v>
       </c>
       <c r="N41" s="3">
         <v>4000</v>
       </c>
       <c r="O41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="P41" s="3">
         <v>6200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>16700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>15600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2900</v>
-      </c>
-      <c r="AG41" s="3">
-        <v>1600</v>
       </c>
       <c r="AH41" s="3">
         <v>1600</v>
       </c>
       <c r="AI41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AJ41" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4099,448 +4189,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E43" s="3">
         <v>48900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>53500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>52300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>50000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>55000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>50500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>57400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>66300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>60600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>67300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>66700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>68800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>52200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>54500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>65300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>63800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>49500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>32600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>35600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>37200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>36900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>33000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>41800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>36500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>30800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>29400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>40100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>35300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>33000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>29300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>36700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E44" s="3">
         <v>77000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>76000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>85500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>86600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>96000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>92500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>105300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>111700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>122500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>121900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>135000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>130200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>114600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>92400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>91800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>86600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>91400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>72500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>63700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>41700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>42200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>42300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>48400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>48000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>47700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>39100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>45700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>41500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>40100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>35200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>42400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>37500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>37200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>33800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2700</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>3000</v>
       </c>
       <c r="AB45" s="3">
         <v>3000</v>
       </c>
       <c r="AC45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AD45" s="3">
         <v>4200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3000</v>
-      </c>
-      <c r="AE45" s="3">
-        <v>2900</v>
       </c>
       <c r="AF45" s="3">
         <v>2900</v>
       </c>
       <c r="AG45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AH45" s="3">
         <v>3400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>4100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127900</v>
+      </c>
+      <c r="E46" s="3">
         <v>131100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>133800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>144700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>139100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>151500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>146800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>175900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>172700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>184000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>188200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>209400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>204300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>201000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>171100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>173600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>154300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>155800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>145400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>136900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>109900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>83600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>86900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>93600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>92500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>88000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>87900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>96300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>90600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>75200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>80300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>82800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>75800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>71900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>75600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4571,8 +4676,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4629,248 +4734,257 @@
         <v>0</v>
       </c>
       <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
         <v>20200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>20300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>19600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>18500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>17400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>19000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E48" s="3">
         <v>23200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>37700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>19800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>17300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>16100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>16400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>15500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>13000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>14200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>13500</v>
-      </c>
-      <c r="AK48" s="3">
-        <v>13700</v>
       </c>
       <c r="AL48" s="3">
         <v>13700</v>
       </c>
+      <c r="AM48" s="3">
+        <v>13700</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E49" s="3">
         <v>67600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>68200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>68700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>69800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>70400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>71600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>72800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>73400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>73900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>74600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>53500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>53900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>54300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>54900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>55300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>44500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>44800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>45300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>45600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>45900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>46300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>45800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>46200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>40200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>40500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>40900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>41200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>41600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>42000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>42500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>42300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4979,8 +5093,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5089,8 +5206,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5098,34 +5218,34 @@
         <v>200</v>
       </c>
       <c r="E52" s="3">
+        <v>200</v>
+      </c>
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2900</v>
       </c>
       <c r="H52" s="3">
         <v>2900</v>
       </c>
       <c r="I52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J52" s="3">
         <v>3000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3200</v>
       </c>
       <c r="M52" s="3">
         <v>3200</v>
       </c>
       <c r="N52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="O52" s="3">
         <v>300</v>
@@ -5134,7 +5254,7 @@
         <v>300</v>
       </c>
       <c r="Q52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R52" s="3">
         <v>100</v>
@@ -5149,10 +5269,10 @@
         <v>100</v>
       </c>
       <c r="V52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X52" s="3">
         <v>100</v>
@@ -5170,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="AC52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -5185,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="AH52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI52" s="3">
         <v>100</v>
@@ -5197,10 +5317,13 @@
         <v>100</v>
       </c>
       <c r="AL52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5309,118 +5432,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>218300</v>
+      </c>
+      <c r="E54" s="3">
         <v>222100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>226300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>244900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>243100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>256300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>253000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>283400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>281100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>293600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>298700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>320300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>316900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>307100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>251800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>254200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>231600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>232000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>220700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>198700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>170900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>145400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>148800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>156000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>155500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>150300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>149500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>149800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>144100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>150200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>156100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>158200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>150200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>145300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>150800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5459,8 +5588,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5499,118 +5629,122 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E57" s="3">
         <v>14300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>12800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>9400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>22700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>25100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>14700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>22700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>20900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>32100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>18100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>6400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>6600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>4400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5621,7 +5755,7 @@
         <v>7600</v>
       </c>
       <c r="F58" s="3">
-        <v>8200</v>
+        <v>7600</v>
       </c>
       <c r="G58" s="3">
         <v>8200</v>
@@ -5636,13 +5770,13 @@
         <v>8200</v>
       </c>
       <c r="K58" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="L58" s="3">
         <v>8100</v>
       </c>
       <c r="M58" s="3">
-        <v>7100</v>
+        <v>8100</v>
       </c>
       <c r="N58" s="3">
         <v>7100</v>
@@ -5662,12 +5796,12 @@
       <c r="S58" s="3">
         <v>7100</v>
       </c>
-      <c r="T58" s="3" t="s">
+      <c r="T58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
@@ -5678,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
         <v>100</v>
@@ -5687,7 +5821,7 @@
         <v>100</v>
       </c>
       <c r="AB58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5699,10 +5833,10 @@
         <v>0</v>
       </c>
       <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AG58" s="3">
-        <v>1300</v>
       </c>
       <c r="AH58" s="3">
         <v>1300</v>
@@ -5717,18 +5851,21 @@
         <v>1300</v>
       </c>
       <c r="AL58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AM58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>8</v>
@@ -5736,11 +5873,11 @@
       <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>400</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
@@ -5751,256 +5888,262 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>22400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>25200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>19200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>25100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>8400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>7100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>11100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>11000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>9700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>12800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E60" s="3">
         <v>32400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>34500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>42000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>30200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>44200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>38900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>49700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>53000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>56100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>48200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>51400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>38400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>37700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>46100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>53200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>33700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>15500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>18200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>14900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>32300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>19500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>22000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>18600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>15100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>18400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E61" s="3">
         <v>17400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>29500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>43400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>54000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>73100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>85000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>96500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>87700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>99600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>94000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>92900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>51900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>42900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>46900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>30100</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -6011,17 +6154,17 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>5200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3700</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -6029,33 +6172,36 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>3800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>21900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>24700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>22400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>23000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>24200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
         <v>300</v>
@@ -6067,7 +6213,7 @@
         <v>300</v>
       </c>
       <c r="H62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I62" s="3">
         <v>400</v>
@@ -6082,58 +6228,58 @@
         <v>400</v>
       </c>
       <c r="M62" s="3">
+        <v>400</v>
+      </c>
+      <c r="N62" s="3">
         <v>13600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4400</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>5100</v>
       </c>
       <c r="AA62" s="3">
         <v>5100</v>
       </c>
       <c r="AB62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AC62" s="3">
         <v>4800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>4500</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>3000</v>
       </c>
       <c r="AE62" s="3">
         <v>3000</v>
@@ -6145,22 +6291,25 @@
         <v>3000</v>
       </c>
       <c r="AH62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI62" s="3">
         <v>5400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>6400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6269,8 +6418,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6379,8 +6531,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6489,118 +6644,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E66" s="3">
         <v>53300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>57300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>74900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>77100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>91600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>88400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>122200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>122700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>137300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>140200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>163000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>160900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>155400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>105200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>109400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>86500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>90100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>81500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>57700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>38300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>20300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>22600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>29900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>28300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>23300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>21200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>19600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>39000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>44400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>52100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>46200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>43100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>49000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6639,8 +6800,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6749,8 +6911,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6859,8 +7024,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6969,8 +7137,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7079,118 +7250,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>165100</v>
+      </c>
+      <c r="E72" s="3">
         <v>165300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>164800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>164200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>160600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>159800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>160100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>147400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>144700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>142600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>144900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>143700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>142400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>138000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>133100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>131200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>131400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>128000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>125200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>126900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>118400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>111100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>112000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>111800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>112800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>112500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>113900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>112000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>110100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>99500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>99900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>94000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>92400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>91600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>91700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7299,8 +7476,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7409,8 +7589,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7519,118 +7702,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>168300</v>
+      </c>
+      <c r="E76" s="3">
         <v>168800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>169000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>170100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>166000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>164700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>164600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>161200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>158400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>156300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>158500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>157300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>156000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>151600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>146600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>144700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>145100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>141900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>139200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>141000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>132600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>125200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>126200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>126100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>127200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>127000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>128300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>126400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>124600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>111200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>111700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>106100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>104100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>102200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>101700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7739,233 +7928,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44751</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44639</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44387</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44275</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44191</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44107</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44023</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43911</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43743</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43659</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43547</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43379</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43295</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43183</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43015</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42931</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42819</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E81" s="3">
         <v>2600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>10200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>300</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>3600</v>
       </c>
       <c r="AD81" s="3">
         <v>3600</v>
       </c>
       <c r="AE81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AF81" s="3">
         <v>12100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8004,8 +8202,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8025,97 +8224,100 @@
         <v>800</v>
       </c>
       <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
         <v>400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>900</v>
       </c>
       <c r="M83" s="3">
         <v>900</v>
       </c>
       <c r="N83" s="3">
+        <v>900</v>
+      </c>
+      <c r="O83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8224,8 +8426,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8334,8 +8539,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8444,8 +8652,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8554,8 +8765,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8664,118 +8878,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E89" s="3">
         <v>3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>10500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>13300</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>20600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-5900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>3900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>8900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>5900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>10300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8814,118 +9034,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-500</v>
       </c>
       <c r="J91" s="3">
         <v>-500</v>
       </c>
       <c r="K91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-1000</v>
       </c>
       <c r="AD91" s="3">
         <v>-1000</v>
       </c>
       <c r="AE91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AK91" s="3">
-        <v>-400</v>
       </c>
       <c r="AL91" s="3">
         <v>-400</v>
       </c>
+      <c r="AM91" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9034,8 +9258,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9144,118 +9371,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>5400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-17800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>34100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9294,8 +9527,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9315,10 +9549,10 @@
         <v>2100</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="J96" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>2100</v>
@@ -9327,7 +9561,7 @@
         <v>2100</v>
       </c>
       <c r="M96" s="3">
-        <v>-2000</v>
+        <v>2100</v>
       </c>
       <c r="N96" s="3">
         <v>-2000</v>
@@ -9339,7 +9573,7 @@
         <v>-2000</v>
       </c>
       <c r="Q96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="R96" s="3">
         <v>-1900</v>
@@ -9348,7 +9582,7 @@
         <v>-1900</v>
       </c>
       <c r="T96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="U96" s="3">
         <v>-2000</v>
@@ -9357,7 +9591,7 @@
         <v>-2000</v>
       </c>
       <c r="W96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="X96" s="3">
         <v>-1800</v>
@@ -9387,7 +9621,7 @@
         <v>-1800</v>
       </c>
       <c r="AG96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AH96" s="3">
         <v>-1700</v>
@@ -9399,13 +9633,16 @@
         <v>-1700</v>
       </c>
       <c r="AK96" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AL96" s="3">
         <v>-1600</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-1600</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9514,8 +9751,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9624,8 +9864,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9734,118 +9977,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-15800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-14000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>40200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>14000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>22800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-7900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-5900</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>1900</v>
       </c>
       <c r="AB100" s="3">
         <v>1900</v>
       </c>
       <c r="AC100" s="3">
-        <v>-1800</v>
+        <v>1900</v>
       </c>
       <c r="AD100" s="3">
         <v>-1800</v>
       </c>
       <c r="AE100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-24300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9876,8 +10125,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9954,114 +10203,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3800</v>
-      </c>
-      <c r="F102" s="3">
-        <v>100</v>
       </c>
       <c r="G102" s="3">
         <v>100</v>
       </c>
       <c r="H102" s="3">
+        <v>100</v>
+      </c>
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2100</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,525 +656,537 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44751</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44639</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44555</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44387</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44275</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44191</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44107</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44023</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43911</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43743</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43659</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43547</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43379</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43295</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43183</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43015</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42931</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42819</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E8" s="3">
         <v>67800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>54300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>55500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>63900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>67700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>62500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>57300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>65500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>73400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>67800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>56900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>72100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>74900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>94300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>72400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>73400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>81300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>99700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>59200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>74800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>78100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>83500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>37300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>47000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>45800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>55600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>32100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>51000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>44000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>48700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>32100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>52200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>41900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>53900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>31900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>49800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E9" s="3">
         <v>48700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>40900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>48000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>50900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>47400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>43000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>49600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>55200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>51100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>45900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>56000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>61300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>70600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>52300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>57100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>63000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>74600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>41800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>56900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>54500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>60300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>27100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>36200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>35700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>42700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>23600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>38800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>31600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>37200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>23200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>40200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>30500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>40800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>23600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>39600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E10" s="3">
         <v>19100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>14400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>18100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>16600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>20100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>17400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>23600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>10200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>10100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>12900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>12200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>12400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>8900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>12000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>11400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>13100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>10200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1215,13 +1227,14 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>3200</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1229,11 +1242,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>3200</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1241,11 +1254,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>3100</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1331,8 +1344,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1447,8 +1463,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1461,14 +1480,14 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-3900</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1485,8 +1504,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1555,16 +1574,19 @@
         <v>0</v>
       </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>-300</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1581,10 +1603,10 @@
         <v>600</v>
       </c>
       <c r="H15" s="3">
+        <v>600</v>
+      </c>
+      <c r="I15" s="3">
         <v>1000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>600</v>
@@ -1602,40 +1624,40 @@
         <v>600</v>
       </c>
       <c r="O15" s="3">
+        <v>600</v>
+      </c>
+      <c r="P15" s="3">
         <v>500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>600</v>
-      </c>
-      <c r="S15" s="3">
-        <v>400</v>
       </c>
       <c r="T15" s="3">
         <v>400</v>
       </c>
       <c r="U15" s="3">
+        <v>400</v>
+      </c>
+      <c r="V15" s="3">
         <v>600</v>
-      </c>
-      <c r="V15" s="3">
-        <v>400</v>
       </c>
       <c r="W15" s="3">
         <v>400</v>
       </c>
       <c r="X15" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y15" s="3">
         <v>300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>400</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>300</v>
       </c>
       <c r="AA15" s="3">
         <v>300</v>
@@ -1644,10 +1666,10 @@
         <v>300</v>
       </c>
       <c r="AC15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD15" s="3">
         <v>500</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>300</v>
       </c>
       <c r="AE15" s="3">
         <v>300</v>
@@ -1656,22 +1678,22 @@
         <v>300</v>
       </c>
       <c r="AG15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH15" s="3">
         <v>400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>300</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>400</v>
       </c>
       <c r="AJ15" s="3">
         <v>400</v>
       </c>
       <c r="AK15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AL15" s="3">
         <v>500</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>400</v>
       </c>
       <c r="AM15" s="3">
         <v>400</v>
@@ -1679,8 +1701,11 @@
       <c r="AN15" s="3">
         <v>400</v>
       </c>
+      <c r="AO15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1718,240 +1743,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E17" s="3">
         <v>60500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>59400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>63700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>58100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>54200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>60500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>66900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>61500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>56800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>67300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>70700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>86100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>63400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>67000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>73600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>89000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>52100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>67800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>65300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>72700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>34900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>43500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>42900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>53200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>31700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>46000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>38800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>46700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>30400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>47100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>37800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>50600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>29600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>46100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E18" s="3">
         <v>7300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>8200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1992,8 +2024,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2001,17 +2034,17 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -2031,25 +2064,25 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -2085,45 +2118,48 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>13100</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>600</v>
       </c>
-      <c r="AK20" s="3">
-        <v>0</v>
-      </c>
       <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E21" s="3">
         <v>7900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>5100</v>
       </c>
       <c r="H21" s="3">
         <v>5100</v>
@@ -2132,100 +2168,103 @@
         <v>5100</v>
       </c>
       <c r="J21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="K21" s="3">
         <v>3700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>5800</v>
       </c>
       <c r="P21" s="3">
         <v>5800</v>
       </c>
       <c r="Q21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="R21" s="3">
         <v>10300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>10500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>8300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>13900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>6100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>16200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>2600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>4700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>3100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>5400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2239,67 +2278,67 @@
         <v>200</v>
       </c>
       <c r="G22" s="3">
+        <v>200</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>500</v>
-      </c>
-      <c r="I22" s="3">
-        <v>700</v>
       </c>
       <c r="J22" s="3">
         <v>700</v>
       </c>
       <c r="K22" s="3">
+        <v>700</v>
+      </c>
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>500</v>
-      </c>
-      <c r="T22" s="3">
-        <v>400</v>
       </c>
       <c r="U22" s="3">
         <v>400</v>
       </c>
       <c r="V22" s="3">
+        <v>400</v>
+      </c>
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
       <c r="AA22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="3">
         <v>100</v>
@@ -2311,13 +2350,13 @@
         <v>100</v>
       </c>
       <c r="AE22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="3">
         <v>200</v>
@@ -2340,240 +2379,249 @@
       <c r="AN22" s="3">
         <v>200</v>
       </c>
+      <c r="AO22" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10300</v>
-      </c>
-      <c r="V23" s="3">
-        <v>6900</v>
       </c>
       <c r="W23" s="3">
         <v>6900</v>
       </c>
       <c r="X23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Y23" s="3">
         <v>12800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>14900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>4500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>3100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>4400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2688,240 +2736,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>5600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>12100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>5600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>8700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>2100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>3500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3036,8 +3093,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3104,17 +3164,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3122,23 +3182,23 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>3000</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3146,14 +3206,17 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AM29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="3" t="s">
+      <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AN29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3268,8 +3331,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3384,8 +3450,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3393,17 +3462,17 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -3423,25 +3492,25 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -3477,147 +3546,153 @@
         <v>0</v>
       </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-600</v>
       </c>
-      <c r="AK32" s="3">
-        <v>0</v>
-      </c>
       <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>5600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>8700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>300</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>3600</v>
       </c>
       <c r="AF33" s="3">
         <v>3600</v>
       </c>
       <c r="AG33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AH33" s="3">
         <v>12100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>2100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>3500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3732,245 +3807,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>5600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>8700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>300</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>3600</v>
       </c>
       <c r="AF35" s="3">
         <v>3600</v>
       </c>
       <c r="AG35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AH35" s="3">
         <v>12100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>2100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>3500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44751</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44639</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44555</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44387</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44275</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44191</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44107</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44023</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43911</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43743</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43659</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43547</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43379</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43295</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43183</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43015</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42931</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42819</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4011,8 +4095,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4053,124 +4138,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E41" s="3">
         <v>3500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4200</v>
-      </c>
-      <c r="H41" s="3">
-        <v>400</v>
       </c>
       <c r="I41" s="3">
         <v>400</v>
       </c>
       <c r="J41" s="3">
+        <v>400</v>
+      </c>
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6100</v>
-      </c>
-      <c r="O41" s="3">
-        <v>4000</v>
       </c>
       <c r="P41" s="3">
         <v>4000</v>
       </c>
       <c r="Q41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R41" s="3">
         <v>6200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>16700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>15600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2900</v>
-      </c>
-      <c r="AI41" s="3">
-        <v>1600</v>
       </c>
       <c r="AJ41" s="3">
         <v>1600</v>
       </c>
       <c r="AK41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AL41" s="3">
         <v>2300</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4285,472 +4374,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E43" s="3">
         <v>52800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>41900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>53500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>52300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>50000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>55000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>50500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>57400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>66300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>60600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>67300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>66700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>68800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>52200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>54500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>65300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>63800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>49500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>32600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>35600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>37200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>36900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>33000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>41800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>36500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>30800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>29400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>40100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>35300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>33000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>29300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>36700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E44" s="3">
         <v>80700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>72700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>77000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>76000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>85500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>86600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>96000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>92500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>105300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>111700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>122500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>121900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>135000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>130200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>114600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>92400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>91800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>86600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>91400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>72500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>63700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>41700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>42200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>42300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>48400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>48000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>47700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>39100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>45700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>41500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>40100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>35200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>42400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>37500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>37200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>33800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>600</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1800</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2700</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>3000</v>
       </c>
       <c r="AD45" s="3">
         <v>3000</v>
       </c>
       <c r="AE45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AF45" s="3">
         <v>4200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>3000</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>2900</v>
       </c>
       <c r="AH45" s="3">
         <v>2900</v>
       </c>
       <c r="AI45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>3400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>3500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>130600</v>
+      </c>
+      <c r="E46" s="3">
         <v>141300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>127900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>131100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>133800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>144700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>139100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>151500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>146800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>175900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>172700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>184000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>188200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>209400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>204300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>201000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>171100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>173600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>154300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>155800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>145400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>136900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>109900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>83600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>86900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>93600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>92500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>88000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>87900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>96300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>90600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>75200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>80300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>82800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>75800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>71900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>75600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4787,8 +4891,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4845,260 +4949,269 @@
         <v>0</v>
       </c>
       <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
         <v>20200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>20300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>19600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>18500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>17400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>19000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23600</v>
+      </c>
+      <c r="E48" s="3">
         <v>23100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>22900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>19800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>17300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>13400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>13900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>13500</v>
-      </c>
-      <c r="AM48" s="3">
-        <v>13700</v>
       </c>
       <c r="AN48" s="3">
         <v>13700</v>
       </c>
+      <c r="AO48" s="3">
+        <v>13700</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E49" s="3">
         <v>68000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>67000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>67600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>68200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>68700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>69800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>70400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>71000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>71600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>72200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>72800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>73400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>73900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>74600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>75000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>53500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>53900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>54300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>54900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>55300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>44500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>44800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>45300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>45600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>45900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>46300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>45800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>46200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>40200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>40500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>40900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>41200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>41600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>42000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>42500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>42300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5213,8 +5326,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5329,13 +5445,16 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>200</v>
@@ -5344,34 +5463,34 @@
         <v>200</v>
       </c>
       <c r="G52" s="3">
+        <v>200</v>
+      </c>
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>2900</v>
       </c>
       <c r="J52" s="3">
         <v>2900</v>
       </c>
       <c r="K52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L52" s="3">
         <v>3000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3300</v>
-      </c>
-      <c r="N52" s="3">
-        <v>3200</v>
       </c>
       <c r="O52" s="3">
         <v>3200</v>
       </c>
       <c r="P52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="Q52" s="3">
         <v>300</v>
@@ -5380,7 +5499,7 @@
         <v>300</v>
       </c>
       <c r="S52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="T52" s="3">
         <v>100</v>
@@ -5395,10 +5514,10 @@
         <v>100</v>
       </c>
       <c r="X52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3">
         <v>100</v>
@@ -5416,7 +5535,7 @@
         <v>100</v>
       </c>
       <c r="AE52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF52" s="3">
         <v>0</v>
@@ -5431,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK52" s="3">
         <v>100</v>
@@ -5443,10 +5562,13 @@
         <v>100</v>
       </c>
       <c r="AN52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AO52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5561,124 +5683,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>222100</v>
+      </c>
+      <c r="E54" s="3">
         <v>232500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>218300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>222100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>226300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>244900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>243100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>256300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>253000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>283400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>281100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>293600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>298700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>320300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>316900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>307100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>251800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>254200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>231600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>232000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>220700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>198700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>170900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>145400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>148800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>156000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>155500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>150300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>149500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>149800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>144100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>150200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>156100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>158200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>150200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>145300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>150800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5719,8 +5847,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5761,129 +5890,133 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E57" s="3">
         <v>21100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>9800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>25100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>22700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>32100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>18100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>6400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>7800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>7800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>5600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>9500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>5200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>9900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>6600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7600</v>
+        <v>7700</v>
       </c>
       <c r="E58" s="3">
         <v>7600</v>
@@ -5895,7 +6028,7 @@
         <v>7600</v>
       </c>
       <c r="H58" s="3">
-        <v>8200</v>
+        <v>7600</v>
       </c>
       <c r="I58" s="3">
         <v>8200</v>
@@ -5910,13 +6043,13 @@
         <v>8200</v>
       </c>
       <c r="M58" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="N58" s="3">
         <v>8100</v>
       </c>
       <c r="O58" s="3">
-        <v>7100</v>
+        <v>8100</v>
       </c>
       <c r="P58" s="3">
         <v>7100</v>
@@ -5936,12 +6069,12 @@
       <c r="U58" s="3">
         <v>7100</v>
       </c>
-      <c r="V58" s="3" t="s">
+      <c r="V58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
         <v>0</v>
       </c>
@@ -5952,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>100</v>
@@ -5961,7 +6094,7 @@
         <v>100</v>
       </c>
       <c r="AD58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE58" s="3">
         <v>0</v>
@@ -5973,10 +6106,10 @@
         <v>0</v>
       </c>
       <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AI58" s="3">
-        <v>1300</v>
       </c>
       <c r="AJ58" s="3">
         <v>1300</v>
@@ -5991,24 +6124,27 @@
         <v>1300</v>
       </c>
       <c r="AN58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AO58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>300</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
@@ -6016,11 +6152,11 @@
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>400</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>8</v>
@@ -6031,268 +6167,274 @@
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P59" s="3">
         <v>22400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>19900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>19200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>25100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>21100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>9500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>7100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>11100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>9700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>7200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E60" s="3">
         <v>42900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>30800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>42000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>30200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>34100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>44200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>32700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>38900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>49700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>53000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>48200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>51400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>38400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>37700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>46100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>53200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>33700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>15500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>18200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>15700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>14900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>16700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>20400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>16600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>32300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>22000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>18600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>15100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>18400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E61" s="3">
         <v>14000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>19200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>29500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>43400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>54000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>51700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>73100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>85000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>96500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>87700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>99600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>94000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>92900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>51900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>42900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>46900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>30100</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -6303,17 +6445,17 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>5200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3700</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -6321,28 +6463,31 @@
         <v>0</v>
       </c>
       <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>3800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>24700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>22400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>23000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>24200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6352,8 +6497,8 @@
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3">
-        <v>300</v>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
@@ -6365,7 +6510,7 @@
         <v>300</v>
       </c>
       <c r="J62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
@@ -6380,58 +6525,58 @@
         <v>400</v>
       </c>
       <c r="O62" s="3">
+        <v>400</v>
+      </c>
+      <c r="P62" s="3">
         <v>13600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>4500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4400</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>5100</v>
       </c>
       <c r="AC62" s="3">
         <v>5100</v>
       </c>
       <c r="AD62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AE62" s="3">
         <v>4800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>4500</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>3000</v>
       </c>
       <c r="AG62" s="3">
         <v>3000</v>
@@ -6443,22 +6588,25 @@
         <v>3000</v>
       </c>
       <c r="AJ62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AK62" s="3">
         <v>5400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>6400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6573,8 +6721,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6689,8 +6840,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6805,124 +6959,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E66" s="3">
         <v>60100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>50000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>57300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>74900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>77100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>88400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>122200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>122700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>137300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>140200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>163000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>160900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>155400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>105200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>109400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>86500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>90100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>81500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>20300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>22600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>29900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>28300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>23300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>21200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>23400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>19600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>39000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>44400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>52100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>46200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>43100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>49000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6963,8 +7123,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7079,8 +7240,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7195,8 +7359,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7311,8 +7478,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7427,124 +7597,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>170200</v>
+      </c>
+      <c r="E72" s="3">
         <v>168600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>165100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>165300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>164800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>164200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>160600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>159800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>160100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>147400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>144700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>142600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>144900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>143700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>142400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>138000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>133100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>131200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>131400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>128000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>125200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>126900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>118400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>111100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>112000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>111800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>112800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>112500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>113900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>112000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>110100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>99500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>99900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>94000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>92400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>91600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>91700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7659,8 +7835,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7775,8 +7954,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7891,124 +8073,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>173200</v>
+      </c>
+      <c r="E76" s="3">
         <v>172300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>168300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>168800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>169000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>170100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>166000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>164700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>164600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>161200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>158400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>156300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>158500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>157300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>156000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>151600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>146600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>144700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>145100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>141900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>139200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>141000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>132600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>125200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>126200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>126100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>127200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>127000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>128300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>126400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>124600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>111200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>111700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>106100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>104100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>102200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>101700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8123,245 +8311,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44751</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44639</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44555</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44387</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44275</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44191</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44107</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44023</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43911</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43743</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43659</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43547</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43379</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43295</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43183</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43015</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42931</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42819</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>5600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>8700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>300</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>3600</v>
       </c>
       <c r="AF81" s="3">
         <v>3600</v>
       </c>
       <c r="AG81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AH81" s="3">
         <v>12100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>2100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>3500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8402,16 +8599,17 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>800</v>
+      </c>
+      <c r="E83" s="3">
         <v>900</v>
-      </c>
-      <c r="E83" s="3">
-        <v>800</v>
       </c>
       <c r="F83" s="3">
         <v>800</v>
@@ -8429,97 +8627,100 @@
         <v>800</v>
       </c>
       <c r="K83" s="3">
+        <v>800</v>
+      </c>
+      <c r="L83" s="3">
         <v>400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>900</v>
       </c>
       <c r="O83" s="3">
         <v>900</v>
       </c>
       <c r="P83" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>1200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>1000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>800</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8634,8 +8835,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8750,8 +8954,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8866,8 +9073,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8982,8 +9192,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9098,124 +9311,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>13300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>10500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>13300</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>20600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>14800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>8400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>9700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>12900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>8900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>7000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>3000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>5900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>10300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9256,124 +9475,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-500</v>
       </c>
       <c r="L91" s="3">
         <v>-500</v>
       </c>
       <c r="M91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-600</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-1000</v>
       </c>
       <c r="AF91" s="3">
         <v>-1000</v>
       </c>
       <c r="AG91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AM91" s="3">
-        <v>-400</v>
       </c>
       <c r="AN91" s="3">
         <v>-400</v>
       </c>
+      <c r="AO91" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9488,8 +9711,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9604,124 +9830,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>5400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>34100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9762,8 +9994,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9789,10 +10022,10 @@
         <v>2100</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="L96" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>2100</v>
@@ -9801,7 +10034,7 @@
         <v>2100</v>
       </c>
       <c r="O96" s="3">
-        <v>-2000</v>
+        <v>2100</v>
       </c>
       <c r="P96" s="3">
         <v>-2000</v>
@@ -9813,7 +10046,7 @@
         <v>-2000</v>
       </c>
       <c r="S96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="T96" s="3">
         <v>-1900</v>
@@ -9822,7 +10055,7 @@
         <v>-1900</v>
       </c>
       <c r="V96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="W96" s="3">
         <v>-2000</v>
@@ -9831,7 +10064,7 @@
         <v>-2000</v>
       </c>
       <c r="Y96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="Z96" s="3">
         <v>-1800</v>
@@ -9861,7 +10094,7 @@
         <v>-1800</v>
       </c>
       <c r="AI96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AJ96" s="3">
         <v>-1700</v>
@@ -9873,13 +10106,16 @@
         <v>-1700</v>
       </c>
       <c r="AM96" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AN96" s="3">
         <v>-1600</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-1600</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9994,8 +10230,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10110,8 +10349,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10226,124 +10468,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-15800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-21100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-14000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>40200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>14000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>22800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5900</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>1900</v>
       </c>
       <c r="AD100" s="3">
         <v>1900</v>
       </c>
       <c r="AE100" s="3">
-        <v>-1800</v>
+        <v>1900</v>
       </c>
       <c r="AF100" s="3">
         <v>-1800</v>
       </c>
       <c r="AG100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-24300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10380,8 +10628,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10458,120 +10706,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3800</v>
-      </c>
-      <c r="H102" s="3">
-        <v>100</v>
       </c>
       <c r="I102" s="3">
         <v>100</v>
       </c>
       <c r="J102" s="3">
+        <v>100</v>
+      </c>
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2100</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ESCA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>ESCA</t>
   </si>
@@ -656,537 +656,550 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44751</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44639</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44387</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44275</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44191</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44107</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44023</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43911</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43827</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43743</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43659</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43547</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43463</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43379</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43295</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43183</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43099</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43015</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42931</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42819</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>55800</v>
+      </c>
+      <c r="E8" s="3">
         <v>62600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>67800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>54300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>63900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>67700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>62500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>57300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>65500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>56900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>72100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>74900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>94300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>72400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>73400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>81300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>99700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>59200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>74800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>78100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>83500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>37300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>47000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>45800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>55600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>32100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>51000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>44000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>48700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>32100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>52200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>41900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>53900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>31900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>49800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E9" s="3">
         <v>45200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>48700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>40900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>50900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>47400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>43000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>49600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>55200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>51100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>45900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>56000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>61300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>70600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>52300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>57100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>63000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>74600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>41800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>56900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>54500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>60300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>27100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>36200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>35700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>42700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>23600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>38800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>31600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>37200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>40200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>30500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>40800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>23600</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>39600</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>28500</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E10" s="3">
         <v>17400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>16600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>23700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>20100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>18300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>25100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>17900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>23600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>23200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>10200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>10800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>10100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>12900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>12200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>12400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>11500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>12000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>11400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>13100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>10200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1228,16 +1241,17 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="3">
         <v>3200</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1245,11 +1259,11 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>3200</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1257,11 +1271,11 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>3100</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1347,8 +1361,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1466,8 +1483,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1483,14 +1503,14 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-3900</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1507,8 +1527,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1577,16 +1597,19 @@
         <v>0</v>
       </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>-300</v>
-      </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1606,10 +1629,10 @@
         <v>600</v>
       </c>
       <c r="I15" s="3">
+        <v>600</v>
+      </c>
+      <c r="J15" s="3">
         <v>1000</v>
-      </c>
-      <c r="J15" s="3">
-        <v>600</v>
       </c>
       <c r="K15" s="3">
         <v>600</v>
@@ -1627,40 +1650,40 @@
         <v>600</v>
       </c>
       <c r="P15" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q15" s="3">
         <v>500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>600</v>
-      </c>
-      <c r="T15" s="3">
-        <v>400</v>
       </c>
       <c r="U15" s="3">
         <v>400</v>
       </c>
       <c r="V15" s="3">
+        <v>400</v>
+      </c>
+      <c r="W15" s="3">
         <v>600</v>
-      </c>
-      <c r="W15" s="3">
-        <v>400</v>
       </c>
       <c r="X15" s="3">
         <v>400</v>
       </c>
       <c r="Y15" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z15" s="3">
         <v>300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>400</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>300</v>
       </c>
       <c r="AB15" s="3">
         <v>300</v>
@@ -1669,10 +1692,10 @@
         <v>300</v>
       </c>
       <c r="AD15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE15" s="3">
         <v>500</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>300</v>
       </c>
       <c r="AF15" s="3">
         <v>300</v>
@@ -1681,22 +1704,22 @@
         <v>300</v>
       </c>
       <c r="AH15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI15" s="3">
         <v>400</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>300</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>400</v>
       </c>
       <c r="AK15" s="3">
         <v>400</v>
       </c>
       <c r="AL15" s="3">
+        <v>400</v>
+      </c>
+      <c r="AM15" s="3">
         <v>500</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>400</v>
       </c>
       <c r="AN15" s="3">
         <v>400</v>
@@ -1704,8 +1727,11 @@
       <c r="AO15" s="3">
         <v>400</v>
       </c>
+      <c r="AP15" s="3">
+        <v>400</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1744,246 +1770,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E17" s="3">
         <v>57400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>60500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>59400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>63700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>58100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>54200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>60500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>66900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>61500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>56800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>67300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>70700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>86100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>63400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>67000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>73600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>89000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>52100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>67800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>65300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>72700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>34900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>43500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>42900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>53200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>31700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>46000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>38800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>46700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>30400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>47100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>37800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>50600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>29600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>46100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>33500</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E18" s="3">
         <v>5200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>8200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>5000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>5200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>5100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3700</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2025,8 +2058,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2037,17 +2071,17 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -2067,25 +2101,25 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -2121,48 +2155,51 @@
         <v>0</v>
       </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>13100</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>600</v>
       </c>
-      <c r="AL20" s="3">
-        <v>0</v>
-      </c>
       <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3">
         <v>-100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E21" s="3">
         <v>5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>5100</v>
       </c>
       <c r="I21" s="3">
         <v>5100</v>
@@ -2171,100 +2208,103 @@
         <v>5100</v>
       </c>
       <c r="K21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L21" s="3">
         <v>3700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>800</v>
-      </c>
-      <c r="P21" s="3">
-        <v>5800</v>
       </c>
       <c r="Q21" s="3">
         <v>5800</v>
       </c>
       <c r="R21" s="3">
+        <v>5800</v>
+      </c>
+      <c r="S21" s="3">
         <v>10300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>10500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>8300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>13900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>6100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>16200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>6800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>5700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>4700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>5400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2281,67 +2321,67 @@
         <v>200</v>
       </c>
       <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>500</v>
-      </c>
-      <c r="J22" s="3">
-        <v>700</v>
       </c>
       <c r="K22" s="3">
         <v>700</v>
       </c>
       <c r="L22" s="3">
+        <v>700</v>
+      </c>
+      <c r="M22" s="3">
         <v>1100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>400</v>
       </c>
       <c r="V22" s="3">
         <v>400</v>
       </c>
       <c r="W22" s="3">
+        <v>400</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>100</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
-      </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
-      </c>
       <c r="AB22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="3">
         <v>100</v>
@@ -2353,13 +2393,13 @@
         <v>100</v>
       </c>
       <c r="AF22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
       </c>
       <c r="AH22" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3">
         <v>200</v>
@@ -2382,246 +2422,255 @@
       <c r="AO22" s="3">
         <v>200</v>
       </c>
+      <c r="AP22" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E23" s="3">
         <v>5000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>8500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>10300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>6900</v>
       </c>
       <c r="X23" s="3">
         <v>6900</v>
       </c>
       <c r="Y23" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z23" s="3">
         <v>12800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>14900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>3100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>4400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2739,246 +2788,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E26" s="3">
         <v>3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>8700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>12100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>2100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E27" s="3">
         <v>3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>8100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>8700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>2100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1400</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3096,8 +3154,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3167,17 +3228,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3185,23 +3246,23 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-600</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>3000</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3209,14 +3270,17 @@
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3334,8 +3398,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3453,8 +3520,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3465,17 +3535,17 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -3495,25 +3565,25 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -3549,150 +3619,156 @@
         <v>0</v>
       </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-600</v>
       </c>
-      <c r="AL32" s="3">
-        <v>0</v>
-      </c>
       <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3">
         <v>100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E33" s="3">
         <v>3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>8100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>8700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>300</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>3600</v>
       </c>
       <c r="AG33" s="3">
         <v>3600</v>
       </c>
       <c r="AH33" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AI33" s="3">
         <v>12100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>7500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>2100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1400</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3810,251 +3886,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E35" s="3">
         <v>3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>8100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>8700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>300</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>3600</v>
       </c>
       <c r="AG35" s="3">
         <v>3600</v>
       </c>
       <c r="AH35" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AI35" s="3">
         <v>12100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>7500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>2100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1400</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44751</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44639</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44387</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44275</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44191</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44107</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44023</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43911</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43827</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43743</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43659</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43547</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43463</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43379</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43295</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43183</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43099</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43015</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42931</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42819</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4096,8 +4181,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4139,127 +4225,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E41" s="3">
         <v>11900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4200</v>
-      </c>
-      <c r="I41" s="3">
-        <v>400</v>
       </c>
       <c r="J41" s="3">
         <v>400</v>
       </c>
       <c r="K41" s="3">
+        <v>400</v>
+      </c>
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
-      </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6100</v>
-      </c>
-      <c r="P41" s="3">
-        <v>4000</v>
       </c>
       <c r="Q41" s="3">
         <v>4000</v>
       </c>
       <c r="R41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S41" s="3">
         <v>6200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>6200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>11100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>15600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2900</v>
-      </c>
-      <c r="AJ41" s="3">
-        <v>1600</v>
       </c>
       <c r="AK41" s="3">
         <v>1600</v>
       </c>
       <c r="AL41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="AM41" s="3">
         <v>2300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4377,484 +4467,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E43" s="3">
         <v>46300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>52800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>41900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>53500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>52300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>50000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>63400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>55000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>50500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>57400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>66300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>60600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>67300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>66700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>68800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>52200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>54500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>65300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>63800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>49500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>32600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>35600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>37200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>36900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>33000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>41800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>36500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>30800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>29400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>40100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>35300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>33000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>29300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>36700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E44" s="3">
         <v>68500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>80700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>72700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>77000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>76000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>85500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>86600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>96000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>92500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>105300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>111700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>122500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>121900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>135000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>130200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>114600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>92400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>91800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>86600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>91400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>72500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>63700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>41700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>42200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>42300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>48400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>48000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>47700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>39100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>45700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>41500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>40100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>35200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>42400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>37500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>37200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>33800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>600</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>2600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>3200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2700</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>3000</v>
       </c>
       <c r="AE45" s="3">
         <v>3000</v>
       </c>
       <c r="AF45" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG45" s="3">
         <v>4200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3000</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>2900</v>
       </c>
       <c r="AI45" s="3">
         <v>2900</v>
       </c>
       <c r="AJ45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AK45" s="3">
         <v>3400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>4100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E46" s="3">
         <v>130600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>141300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>127900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>131100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>133800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>144700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>139100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>151500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>146800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>175900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>172700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>184000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>188200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>209400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>204300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>201000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>171100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>173600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>154300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>155800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>145400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>136900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>109900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>83600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>86900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>93600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>92500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>88000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>87900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>96300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>90600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>75200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>80300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>82800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>75800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>71900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>75600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>89700</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4894,8 +4999,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4952,266 +5057,275 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>20200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>20300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>19600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>18500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>17400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>19000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E48" s="3">
         <v>23600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>33900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>30700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>27100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>22900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>19800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>17300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>16400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>13400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>14300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>14200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>13900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>13500</v>
-      </c>
-      <c r="AN48" s="3">
-        <v>13700</v>
       </c>
       <c r="AO48" s="3">
         <v>13700</v>
       </c>
+      <c r="AP48" s="3">
+        <v>13700</v>
+      </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67200</v>
+      </c>
+      <c r="E49" s="3">
         <v>67800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>68000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>67000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>67600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>68200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>68700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>69800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>70400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>71000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>71600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>72200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>72800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>73400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>73900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>74600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>75000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>53500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>53900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>54300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>54900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>55300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>44500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>44800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>45300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>45600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>45900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>46300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>45800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>46200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>40200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>40500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>40900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>41200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>41600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>42000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>42500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>42300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>42700</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5329,8 +5443,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5448,16 +5565,19 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>200</v>
       </c>
       <c r="F52" s="3">
         <v>200</v>
@@ -5466,34 +5586,34 @@
         <v>200</v>
       </c>
       <c r="H52" s="3">
+        <v>200</v>
+      </c>
+      <c r="I52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>2900</v>
       </c>
       <c r="K52" s="3">
         <v>2900</v>
       </c>
       <c r="L52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3300</v>
-      </c>
-      <c r="O52" s="3">
-        <v>3200</v>
       </c>
       <c r="P52" s="3">
         <v>3200</v>
       </c>
       <c r="Q52" s="3">
-        <v>300</v>
+        <v>3200</v>
       </c>
       <c r="R52" s="3">
         <v>300</v>
@@ -5502,7 +5622,7 @@
         <v>300</v>
       </c>
       <c r="T52" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U52" s="3">
         <v>100</v>
@@ -5517,10 +5637,10 @@
         <v>100</v>
       </c>
       <c r="Y52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3">
         <v>100</v>
@@ -5538,7 +5658,7 @@
         <v>100</v>
       </c>
       <c r="AF52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG52" s="3">
         <v>0</v>
@@ -5553,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL52" s="3">
         <v>100</v>
@@ -5565,10 +5685,13 @@
         <v>100</v>
       </c>
       <c r="AO52" s="3">
+        <v>100</v>
+      </c>
+      <c r="AP52" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5686,127 +5809,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>227600</v>
+      </c>
+      <c r="E54" s="3">
         <v>222100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>232500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>218300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>222100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>226300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>244900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>243100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>256300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>253000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>283400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>281100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>293600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>298700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>320300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>316900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>251800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>254200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>231600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>232000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>220700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>198700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>170900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>145400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>148800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>156000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>155500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>150300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>149500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>149800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>144100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>150200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>156100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>158200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>150200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>145300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>150800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>165300</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5848,8 +5977,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5891,135 +6021,139 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E57" s="3">
         <v>9200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>21100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>24700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>25100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>22700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>32100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>18100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>7200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>7800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>5600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>9500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>5200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>4300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>9900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>8000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>6600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>4400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E58" s="3">
         <v>7700</v>
-      </c>
-      <c r="E58" s="3">
-        <v>7600</v>
       </c>
       <c r="F58" s="3">
         <v>7600</v>
@@ -6031,7 +6165,7 @@
         <v>7600</v>
       </c>
       <c r="I58" s="3">
-        <v>8200</v>
+        <v>7600</v>
       </c>
       <c r="J58" s="3">
         <v>8200</v>
@@ -6046,13 +6180,13 @@
         <v>8200</v>
       </c>
       <c r="N58" s="3">
-        <v>8100</v>
+        <v>8200</v>
       </c>
       <c r="O58" s="3">
         <v>8100</v>
       </c>
       <c r="P58" s="3">
-        <v>7100</v>
+        <v>8100</v>
       </c>
       <c r="Q58" s="3">
         <v>7100</v>
@@ -6072,12 +6206,12 @@
       <c r="V58" s="3">
         <v>7100</v>
       </c>
-      <c r="W58" s="3" t="s">
+      <c r="W58" s="3">
+        <v>7100</v>
+      </c>
+      <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
@@ -6088,7 +6222,7 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>100</v>
@@ -6097,7 +6231,7 @@
         <v>100</v>
       </c>
       <c r="AE58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF58" s="3">
         <v>0</v>
@@ -6109,10 +6243,10 @@
         <v>0</v>
       </c>
       <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>18900</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>1300</v>
       </c>
       <c r="AK58" s="3">
         <v>1300</v>
@@ -6127,27 +6261,30 @@
         <v>1300</v>
       </c>
       <c r="AO58" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AP58" s="3">
         <v>32100</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>300</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
@@ -6155,11 +6292,11 @@
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>400</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>8</v>
@@ -6170,274 +6307,280 @@
       <c r="O59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="3">
         <v>22400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>19900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>25200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>19200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>25100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>9500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>7100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>11100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>9700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>10800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>9200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>7200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>12800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>44600</v>
+      </c>
+      <c r="E60" s="3">
         <v>30500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>42900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>30800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>32400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>42000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>30200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>44200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>32700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>35900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>38900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>49700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>53000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>56100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>48200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>51400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>38400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>37700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>46100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>53200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>33700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>18200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>15700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>14900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>16700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>20400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>16600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>32300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>19500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>22000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>18600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>15100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>18400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>52200</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
         <v>12100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>15900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>29500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>43400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>54000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>51700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>73100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>85000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>96500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>87700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>99600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>94000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>92900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>50400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>51900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>42900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>46900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>30100</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -6448,17 +6591,17 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>5200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3700</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
@@ -6466,28 +6609,31 @@
         <v>0</v>
       </c>
       <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>21900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>24700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>22400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>23000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>24200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6500,8 +6646,8 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
-        <v>300</v>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
         <v>300</v>
@@ -6513,7 +6659,7 @@
         <v>300</v>
       </c>
       <c r="K62" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
@@ -6528,58 +6674,58 @@
         <v>400</v>
       </c>
       <c r="P62" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q62" s="3">
         <v>13600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>5500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>4500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>4600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>4800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>4400</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>5100</v>
       </c>
       <c r="AD62" s="3">
         <v>5100</v>
       </c>
       <c r="AE62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AF62" s="3">
         <v>4800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>4500</v>
-      </c>
-      <c r="AG62" s="3">
-        <v>3000</v>
       </c>
       <c r="AH62" s="3">
         <v>3000</v>
@@ -6591,22 +6737,25 @@
         <v>3000</v>
       </c>
       <c r="AK62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AL62" s="3">
         <v>5400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>6400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6724,8 +6873,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6843,8 +6995,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6962,127 +7117,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E66" s="3">
         <v>48900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>50000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>57300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>74900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>91600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>88400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>122200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>122700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>137300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>140200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>163000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>160900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>155400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>105200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>109400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>86500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>90100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>81500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>57700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>38300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>20300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>22600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>28300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>23300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>21200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>23400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>19600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>39000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>44400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>52100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>46200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>43100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>49000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>64600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7124,8 +7285,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7243,8 +7405,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7362,8 +7527,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7481,8 +7649,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7600,127 +7771,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E72" s="3">
         <v>170200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>168600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>165100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>165300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>164800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>164200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>160600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>159800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>160100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>147400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>144700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>142600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>144900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>143700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>142400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>138000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>133100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>131200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>131400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>128000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>125200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>126900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>118400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>111100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>112000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>111800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>112800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>112500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>113900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>112000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>110100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>99500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>99900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>94000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>92400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>91600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>91700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>89600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7838,8 +8015,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7957,8 +8137,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8076,127 +8259,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>175800</v>
+      </c>
+      <c r="E76" s="3">
         <v>173200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>172300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>168300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>168800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>169000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>170100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>166000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>164700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>164600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>161200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>158400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>156300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>158500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>157300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>156000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>151600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>146600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>144700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>145100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>141900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>139200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>141000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>132600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>125200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>126200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>126100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>127200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>127000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>128300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>126400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>124600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>111200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>111700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>106100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>104100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>102200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>101700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>100600</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8314,251 +8503,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44751</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44639</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44387</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44275</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44191</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44107</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44023</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43911</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43827</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43743</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43659</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43547</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43463</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43379</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43295</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43183</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43099</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43015</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42931</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42819</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E81" s="3">
         <v>3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>8100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>8700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>300</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>3600</v>
       </c>
       <c r="AG81" s="3">
         <v>3600</v>
       </c>
       <c r="AH81" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AI81" s="3">
         <v>12100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>7500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>2100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1400</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8600,19 +8798,20 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>800</v>
       </c>
       <c r="G83" s="3">
         <v>800</v>
@@ -8630,97 +8829,100 @@
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
         <v>400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>900</v>
       </c>
       <c r="P83" s="3">
         <v>900</v>
       </c>
       <c r="Q83" s="3">
+        <v>900</v>
+      </c>
+      <c r="R83" s="3">
         <v>1600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>1200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>1000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>800</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8838,8 +9040,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8957,8 +9162,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9076,8 +9284,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9195,8 +9406,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9314,127 +9528,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E89" s="3">
         <v>14900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>13300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>10500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>13300</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>20600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>8400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-2600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>9700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>12900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>8900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>7000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>5900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>10300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-2500</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9476,127 +9696,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-400</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-500</v>
       </c>
       <c r="M91" s="3">
         <v>-500</v>
       </c>
       <c r="N91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-1000</v>
       </c>
       <c r="AG91" s="3">
         <v>-1000</v>
       </c>
       <c r="AH91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AN91" s="3">
-        <v>-400</v>
       </c>
       <c r="AO91" s="3">
         <v>-400</v>
       </c>
+      <c r="AP91" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9714,8 +9938,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9833,127 +10060,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>34100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9995,8 +10228,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10025,10 +10259,10 @@
         <v>2100</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="M96" s="3">
-        <v>2100</v>
+        <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>2100</v>
@@ -10037,7 +10271,7 @@
         <v>2100</v>
       </c>
       <c r="P96" s="3">
-        <v>-2000</v>
+        <v>2100</v>
       </c>
       <c r="Q96" s="3">
         <v>-2000</v>
@@ -10049,7 +10283,7 @@
         <v>-2000</v>
       </c>
       <c r="T96" s="3">
-        <v>-1900</v>
+        <v>-2000</v>
       </c>
       <c r="U96" s="3">
         <v>-1900</v>
@@ -10058,7 +10292,7 @@
         <v>-1900</v>
       </c>
       <c r="W96" s="3">
-        <v>-2000</v>
+        <v>-1900</v>
       </c>
       <c r="X96" s="3">
         <v>-2000</v>
@@ -10067,7 +10301,7 @@
         <v>-2000</v>
       </c>
       <c r="Z96" s="3">
-        <v>-1800</v>
+        <v>-2000</v>
       </c>
       <c r="AA96" s="3">
         <v>-1800</v>
@@ -10097,7 +10331,7 @@
         <v>-1800</v>
       </c>
       <c r="AJ96" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AK96" s="3">
         <v>-1700</v>
@@ -10109,13 +10343,16 @@
         <v>-1700</v>
       </c>
       <c r="AN96" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="AO96" s="3">
         <v>-1600</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-1600</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10233,8 +10470,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10352,8 +10592,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10471,127 +10714,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-15800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>40200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>14000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>22800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5900</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>1900</v>
       </c>
       <c r="AE100" s="3">
         <v>1900</v>
       </c>
       <c r="AF100" s="3">
-        <v>-1800</v>
+        <v>1900</v>
       </c>
       <c r="AG100" s="3">
         <v>-1800</v>
       </c>
       <c r="AH100" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-24300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-2100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-13500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10631,8 +10880,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10709,123 +10958,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E102" s="3">
         <v>8400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3800</v>
-      </c>
-      <c r="I102" s="3">
-        <v>100</v>
       </c>
       <c r="J102" s="3">
         <v>100</v>
       </c>
       <c r="K102" s="3">
+        <v>100</v>
+      </c>
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2100</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>10500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>12700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>1500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-3300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1000</v>
       </c>
     </row>
